--- a/docs/downloads/Cambridge.xlsx
+++ b/docs/downloads/Cambridge.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D241"/>
+  <dimension ref="A1:D306"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -457,17 +457,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sherwin</t>
+          <t>Natasha</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cruz</t>
+          <t>Saunders</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sherwincruz297@gmail.com</t>
+          <t>natashalsaunders@gmail.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,17 +479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Sherwin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Cruz</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nathan342@rogers.com</t>
+          <t>sherwincruz297@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -501,17 +501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bulmer</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>joshbulmer@live.com</t>
+          <t>nathan342@rogers.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,17 +523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Truax</t>
+          <t>Bulmer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dtruax72@gmail.com</t>
+          <t>joshbulmer@live.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Benoit</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bourgault</t>
+          <t>Truax</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>gotyourmessage@gmail.com</t>
+          <t>dtruax72@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ramit</t>
+          <t>Benoit</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Raj</t>
+          <t>Bourgault</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ramit@pickleplexclub.ca</t>
+          <t>gotyourmessage@gmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vinh</t>
+          <t>Pauline</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ly</t>
+          <t>Szeto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vinhly68@hotmail.com</t>
+          <t>paulines_5@hotmail.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Ramit</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Waring</t>
+          <t>Raj</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tinalwaring@gmail.com</t>
+          <t>ramit@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -633,17 +633,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Milja</t>
+          <t>Audrie</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gillespie</t>
+          <t>Bouwmeester</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>miljagillespie@gmail.com</t>
+          <t>audriebouwmeester@live.ca</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -655,17 +655,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hannay</t>
+          <t>Waring</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>shannay@rogers.com</t>
+          <t>tinalwaring@gmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -677,17 +677,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Maddie</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lena28ca@yahoo.com</t>
+          <t>fc8833@yahoo.ca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -699,17 +699,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Milja</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Truax</t>
+          <t>Gillespie</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dltruax@rogers.com</t>
+          <t>miljagillespie@gmail.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -721,17 +721,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kesselring</t>
+          <t>Hannay</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>timkesselring33@gmail.com</t>
+          <t>shannay@rogers.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,17 +743,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Maddie</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>phrednlare@hotmail.com</t>
+          <t>lena28ca@yahoo.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -765,17 +765,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Couch</t>
+          <t>Truax</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ajcouch2021@gmail.com</t>
+          <t>dltruax@rogers.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Katie</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>katiekesselring@gmail.com</t>
+          <t>timkesselring33@gmail.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -809,17 +809,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kamil</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Machnik</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>kamil.machnik@hotmail.com</t>
+          <t>phrednlare@hotmail.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,17 +831,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rev</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jayakumar</t>
+          <t>Couch</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>revjk18@gmail.com</t>
+          <t>ajcouch2021@gmail.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mercier</t>
+          <t>Kesselring</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dalemercier6193@gmail.com</t>
+          <t>katiekesselring@gmail.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -875,17 +875,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Blair</t>
+          <t>Kamil</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mcdonald</t>
+          <t>Machnik</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>blairmcdonald.ca@gmail.com</t>
+          <t>kamil.machnik@hotmail.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -897,17 +897,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bojan</t>
+          <t>Rev</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Batricevic</t>
+          <t>Jayakumar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>bojanbatricevic@gmail.com</t>
+          <t>revjk18@gmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -919,17 +919,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Asif</t>
+          <t>Dale</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Alidina</t>
+          <t>Mercier</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>asif+@pickleplexclub.ca</t>
+          <t>dalemercier6193@gmail.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -941,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Blair</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Mcdonald</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ksbailey@yahoo.com</t>
+          <t>blairmcdonald.ca@gmail.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Bojan</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Bridgman</t>
+          <t>Batricevic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>susan_bridge@live.ca</t>
+          <t>bojanbatricevic@gmail.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Siya</t>
+          <t>Asif</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sood</t>
+          <t>Alidina</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>siyasood1107@gmail.com</t>
+          <t>asif+@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Polzin</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>polzinlandscaping@me.com</t>
+          <t>ksbailey@yahoo.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1029,17 +1029,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pat</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grasso</t>
+          <t>Bridgman</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>pat.grasso@togers.com</t>
+          <t>susan_bridge@live.ca</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nghia</t>
+          <t>Siya</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Duong</t>
+          <t>Sood</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nghiadduong@gmail.com</t>
+          <t>siyasood1107@gmail.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sponder</t>
+          <t>Polzin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>chris.sponder@gmail.com</t>
+          <t>polzinlandscaping@me.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pickleplex</t>
+          <t>Rawn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>cambridge@pickleplexclub.ca</t>
+          <t>brycerawn18@gmail.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bradshaw</t>
+          <t>Csaszar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>abradshaw435@gmail.com</t>
+          <t>matthewcsaszar@gmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Pat</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Juniper</t>
+          <t>Grasso</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>maureen@praxispr.ca</t>
+          <t>pat.grasso@togers.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Nghia</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alviano</t>
+          <t>Duong</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>lisaa@rogers.com</t>
+          <t>nghiadduong@gmail.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dean</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Sponder</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>deanjmac@yahoo.ca</t>
+          <t>chris.sponder@gmail.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Pickleplex</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jay@pickleplexclub.ca</t>
+          <t>cambridge@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Yong</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Bradshaw</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>yon_liu@hotmail.com</t>
+          <t>abradshaw435@gmail.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Leiskau</t>
+          <t>Juniper</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>kara@jdgraphics.com</t>
+          <t>maureen@praxispr.ca</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,15 +1271,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Devanshi</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mistry</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Alviano</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>lisaa@rogers.com</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1289,15 +1293,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Beckett</t>
+          <t>Dean</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>Macdonald</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>deanjmac@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1307,15 +1315,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jay@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1325,15 +1337,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Amaya</t>
+          <t>Yong</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ismail</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>yon_liu@hotmail.com</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1343,15 +1359,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Paige</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pilkey</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>Leiskau</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>kara@jdgraphics.com</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1361,12 +1381,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Finnley</t>
+          <t>Devanshi</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Mistry</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1379,12 +1399,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Beckett</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pilkey</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1397,7 +1417,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marigold</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1415,12 +1435,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Amaya</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Kollar</t>
+          <t>Ismail</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1433,12 +1453,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kavir</t>
+          <t>Paige</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Pilkey</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1451,12 +1471,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Finnley</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pilkey</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1469,12 +1489,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Anise</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ismail</t>
+          <t>Pilkey</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1487,12 +1507,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Silas</t>
+          <t>Marigold</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pharoah</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1505,19 +1525,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hilda</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Dusek</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>mhdudek@gmail.com</t>
-        </is>
-      </c>
+          <t>Kollar</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1527,12 +1543,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Verne</t>
+          <t>Kavir</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pharoah</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1545,12 +1561,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Souza Cefrin da Silva</t>
+          <t>Pilkey</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1563,12 +1579,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Wesley</t>
+          <t>Anise</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Yuricek</t>
+          <t>Ismail</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1581,12 +1597,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sayali</t>
+          <t>Silas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Parkhi</t>
+          <t>Pharoah</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1599,15 +1615,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gabby</t>
+          <t>Hilda</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Dusek</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>mhdudek@gmail.com</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1617,12 +1637,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Verne</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>Pharoah</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1635,12 +1655,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Rhonda</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kalverda</t>
+          <t>Souza Cefrin da Silva</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1653,12 +1673,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Reagan</t>
+          <t>Wesley</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Yuricek</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1671,12 +1691,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Sayali</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>Parkhi</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1689,12 +1709,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Gabby</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Yuricek</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1707,12 +1727,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Devan</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bhatt</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1725,12 +1745,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>Rhonda</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>Kalverda</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1743,12 +1763,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Reagan</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stead</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1761,12 +1781,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hicks</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1779,12 +1799,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Armen</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Kabakian</t>
+          <t>Yuricek</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1797,12 +1817,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kaiya</t>
+          <t>Devan</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>Bhatt</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1815,12 +1835,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Greyson</t>
+          <t>brian</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>le</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1833,12 +1853,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>Stead</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1851,12 +1871,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ottman</t>
+          <t>Hicks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1869,12 +1889,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Grayson</t>
+          <t>Armen</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Taneza</t>
+          <t>Kabakian</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1887,12 +1907,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Kaiya</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1905,12 +1925,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Greyson</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1923,12 +1943,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Valeria</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mencia</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1941,19 +1961,15 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>De almeida</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>daniel.abeldealmeida@gmail.com</t>
-        </is>
-      </c>
+          <t>Ottman</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1963,12 +1979,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Grayson</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jauregui</t>
+          <t>Taneza</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1981,12 +1997,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Dandrea</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1999,12 +2015,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Diaz</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2017,12 +2033,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ripley</t>
+          <t>Valeria</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Matheson</t>
+          <t>Mencia</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2035,17 +2051,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Jean-paul</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Morgan</t>
+          <t>De almeida</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>morganjea18@gmail.com</t>
+          <t>daniel.abeldealmeida@gmail.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2057,12 +2073,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>POOJA</t>
+          <t>Cesar</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pawar</t>
+          <t>Jauregui</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2075,12 +2091,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Neel</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Gondalia</t>
+          <t>Dandrea</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -2093,12 +2109,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sharp</t>
+          <t>Diaz</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2111,12 +2127,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Ripley</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Matheson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2129,15 +2145,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Jean-paul</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Duong</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>Morgan</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>morganjea18@gmail.com</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2147,12 +2167,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>POOJA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Pawar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2165,12 +2185,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Clara</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Gondalia</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2183,12 +2203,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Maxwell</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mondor</t>
+          <t>Sharp</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2201,12 +2221,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>McDonald</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2219,19 +2239,15 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>5116rpb@gmail.com</t>
-        </is>
-      </c>
+          <t>Duong</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2241,12 +2257,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Beck</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2259,12 +2275,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Nora</t>
+          <t>Clara</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Mondor</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2277,12 +2293,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Payton</t>
+          <t>Maxwell</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Marr</t>
+          <t>Mondor</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2295,12 +2311,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Raphael</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
+          <t>McDonald</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2313,17 +2329,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>rplayer.4050@gmail.com</t>
+          <t>5116rpb@gmail.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -2335,12 +2351,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Coelho</t>
+          <t>Beck</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2353,19 +2369,15 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Will</t>
+          <t>Nora</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Law</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>solis.environmental@gmail.com</t>
-        </is>
-      </c>
+          <t>Mondor</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2375,12 +2387,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Payton</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Coelho</t>
+          <t>Marr</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2393,12 +2405,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Raphael</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Player</t>
+          <t>Del Rosario</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2411,15 +2423,19 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Coelho</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>rplayer.4050@gmail.com</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2429,12 +2445,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2447,15 +2463,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>King</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>Law</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>solis.environmental@gmail.com</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2465,12 +2485,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ballard</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2483,12 +2503,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Prachi</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2501,12 +2521,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rolleman</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2519,12 +2539,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2537,12 +2557,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Katrina</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>King</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2555,12 +2575,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Elissa</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Ballard</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2573,12 +2593,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Suzy</t>
+          <t>Prachi</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2591,12 +2611,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Huo</t>
+          <t>Rolleman</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2609,12 +2629,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>King</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2627,12 +2647,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Katrina</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Snook</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2645,12 +2665,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Jobathan</t>
+          <t>Elissa</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Huo</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2663,7 +2683,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Suzy</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2681,7 +2701,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2699,12 +2719,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2717,12 +2737,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Fry</t>
+          <t>Snook</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2735,12 +2755,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Jobathan</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lannutti</t>
+          <t>Huo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2753,19 +2773,15 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Jasper</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Viado</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>jasper@pickleplexclub.ca</t>
-        </is>
-      </c>
+          <t>Ioannou</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2775,12 +2791,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Huehn</t>
+          <t>Huo</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2793,19 +2809,15 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Dhuha</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Chaudhry</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>dhuha123@live.ca</t>
-        </is>
-      </c>
+          <t>Ioannou</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2815,12 +2827,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Declan</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Huehn</t>
+          <t>Fry</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2833,12 +2845,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Lacey</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Huehn</t>
+          <t>Lannutti</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2851,15 +2863,19 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Jasper</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ritchie</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
+          <t>Viado</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>jasper@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2869,12 +2885,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ritchie</t>
+          <t>Huehn</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2887,17 +2903,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Morgan</t>
+          <t>Dhuha</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Mcallister</t>
+          <t>Chaudhry</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>josh027girl@gmail.com</t>
+          <t>dhuha123@live.ca</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2909,12 +2925,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Declan</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Hardy</t>
+          <t>Huehn</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2927,12 +2943,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Lacey</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>An</t>
+          <t>Huehn</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -2945,12 +2961,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Ritchie</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2963,12 +2979,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Eliot</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Ritchie</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2981,15 +2997,19 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Elliott</t>
+          <t>Morgan</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Hardy</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr"/>
+          <t>Mcallister</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>josh027girl@gmail.com</t>
+        </is>
+      </c>
       <c r="D132" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2999,12 +3019,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Kerr</t>
+          <t>Hardy</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3017,19 +3037,15 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Amaral</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>jameralc522@rogers.com</t>
-        </is>
-      </c>
+          <t>An</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3039,19 +3055,15 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Kharodia</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>zohra_kharodia@hotmail.com</t>
-        </is>
-      </c>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3061,12 +3073,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Eliot</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kerr</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3079,19 +3091,15 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sheila</t>
+          <t>Elliott</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Anonuevo</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>sheila.anonuevo@gmail.com</t>
-        </is>
-      </c>
+          <t>Hardy</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3101,19 +3109,15 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Guest</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>guest123$@hotmail.com</t>
-        </is>
-      </c>
+          <t>Kerr</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3123,17 +3127,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mufaddal</t>
+          <t>Joe</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Jerwalla</t>
+          <t>Amaral</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>mufaddaljerwalla@gmail.com</t>
+          <t>jameralc522@rogers.com</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -3145,15 +3149,19 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>Kharodia</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>zohra_kharodia@hotmail.com</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3163,12 +3171,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Grady</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>More</t>
+          <t>Kerr</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3181,17 +3189,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Caroleann</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Fleming</t>
+          <t>Sandhu</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>carbyckshank@bell.net</t>
+          <t>jay@registon.ca</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3203,15 +3211,19 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Gwen</t>
+          <t>Sheila</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Dias</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr"/>
+          <t>Anonuevo</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>sheila.anonuevo@gmail.com</t>
+        </is>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3221,15 +3233,19 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Jaxon</t>
+          <t>Guest</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Vacon</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr"/>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>guest123$@hotmail.com</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3239,17 +3255,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Mufaddal</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Phan</t>
+          <t>Jerwalla</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>phanmyster@gmail.com</t>
+          <t>mufaddaljerwalla@gmail.com</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3261,12 +3277,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3279,12 +3295,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Grady</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Reiber</t>
+          <t>More</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3297,15 +3313,19 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Caroleann</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sayavong</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
+          <t>Fleming</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>carbyckshank@bell.net</t>
+        </is>
+      </c>
       <c r="D148" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3315,19 +3335,15 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Gwen</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Thirtle</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>sthirtle@rogers.com</t>
-        </is>
-      </c>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3337,12 +3353,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Jaxon</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Lockner</t>
+          <t>Vacon</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3355,15 +3371,19 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Milo</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Moodley</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
+          <t>Phan</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>phanmyster@gmail.com</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3373,17 +3393,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Elie</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Walls</t>
+          <t>Daccache</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>abbydeane05@icloud.com</t>
+          <t>d.elie@ymail.com</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -3395,19 +3415,15 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Walls</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>shanny.deane@gmail.com</t>
-        </is>
-      </c>
+          <t>Ferguson</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3417,19 +3433,15 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Nafisa</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Unia</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>nafisaunia1971@gmail.com</t>
-        </is>
-      </c>
+          <t>Reiber</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3439,19 +3451,15 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Elsden</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>maxelsden@gmail.com</t>
-        </is>
-      </c>
+          <t>Sayavong</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3461,17 +3469,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Cymbalski</t>
+          <t>Thirtle</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>john.cymbalski@gmail.com</t>
+          <t>sthirtle@rogers.com</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -3483,19 +3491,15 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Dawe</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>rtdawe@icloud.com</t>
-        </is>
-      </c>
+          <t>Lockner</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3505,19 +3509,15 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Arul</t>
+          <t>Milo</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Kumar</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>dinsboyjr@gmail.com</t>
-        </is>
-      </c>
+          <t>Moodley</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3527,17 +3527,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Vedansh</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Kokra</t>
+          <t>Walls</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>vedansh.kokra@icloud.com</t>
+          <t>abbydeane05@icloud.com</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3549,17 +3549,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Elisabeth</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Eden</t>
+          <t>Walls</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>elisabeth.eden12@gmail.com</t>
+          <t>shanny.deane@gmail.com</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -3571,17 +3571,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Nafisa</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Genovese</t>
+          <t>Unia</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>genoveseron9@gmail.com</t>
+          <t>nafisaunia1971@gmail.com</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3593,17 +3593,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Zachary</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Janzen</t>
+          <t>Elsden</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>zacharyj115@gmail.com</t>
+          <t>maxelsden@gmail.com</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3615,17 +3615,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Mabel</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Dawe</t>
+          <t>Cymbalski</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>mabeldawe@msn.com</t>
+          <t>john.cymbalski@gmail.com</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3637,17 +3637,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Shah</t>
+          <t>Dawe</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>advaitshah323@gmail.com</t>
+          <t>rtdawe@icloud.com</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3659,17 +3659,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Connie</t>
+          <t>Arul</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Parsons</t>
+          <t>Kumar</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>david.parsons4@sympatico.ca</t>
+          <t>dinsboyjr@gmail.com</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3681,17 +3681,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Vedansh</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Yang - t</t>
+          <t>Kokra</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>yang.julie519@trial.ca</t>
+          <t>vedansh.kokra@icloud.com</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3703,17 +3703,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>elisabeth</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Maier</t>
+          <t>eden</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>shannonmaier@gmail.com</t>
+          <t>elisabeth.eden12@gmail.com</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3725,17 +3725,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Awakian</t>
+          <t>Genovese</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>jack@tricityflooring.ca</t>
+          <t>genoveseron9@gmail.com</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3747,15 +3747,19 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Macy</t>
+          <t>Zachary</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
+          <t>Janzen</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>zacharyj115@gmail.com</t>
+        </is>
+      </c>
       <c r="D169" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3765,15 +3769,19 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ainsworth</t>
+          <t>Mabel</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
+          <t>Dawe</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>mabeldawe@msn.com</t>
+        </is>
+      </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3783,15 +3791,19 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ainsley</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
+          <t>Shah</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>advaitshah323@gmail.com</t>
+        </is>
+      </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3801,15 +3813,19 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Inaya</t>
+          <t>Connie</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Sajid</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>Parsons</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>david.parsons4@sympatico.ca</t>
+        </is>
+      </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3819,15 +3835,19 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Zayan</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Sajid</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr"/>
+          <t>Yang - t</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>yang.julie519@trial.ca</t>
+        </is>
+      </c>
       <c r="D173" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3837,15 +3857,19 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Giselle</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr"/>
+          <t>Maier</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>shannonmaier@gmail.com</t>
+        </is>
+      </c>
       <c r="D174" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3855,15 +3879,19 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Waring</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr"/>
+          <t>Awakian</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>jack@tricityflooring.ca</t>
+        </is>
+      </c>
       <c r="D175" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3873,12 +3901,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Macy</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3891,12 +3919,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Rian</t>
+          <t>Ainsworth</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3909,12 +3937,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Tesia</t>
+          <t>Ainsley</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C178" t="inlineStr"/>
@@ -3927,19 +3955,15 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Elisabeth</t>
+          <t>Inaya</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Bajet</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>eilbajet@gmail.com</t>
-        </is>
-      </c>
+          <t>Sajid</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3949,19 +3973,15 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Tailem</t>
+          <t>Zayan</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Gingras</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>tag2005@icloud.com</t>
-        </is>
-      </c>
+          <t>Sajid</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3971,19 +3991,15 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>jill</t>
+          <t>Giselle</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>singleton</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>guest.guest@gmail.com</t>
-        </is>
-      </c>
+          <t>Del Rosario</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3993,19 +4009,15 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Blacker</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>blacker.shannon@gmail.com</t>
-        </is>
-      </c>
+          <t>Waring</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4015,19 +4027,15 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Furtado</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>sydneyfurtado06@gmail.com</t>
-        </is>
-      </c>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4037,19 +4045,15 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Rian</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Bauer</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>hikeradk04@yahoo.com</t>
-        </is>
-      </c>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4059,19 +4063,15 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Tesia</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Perryman</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>sandyperryman59#1@gmail.com</t>
-        </is>
-      </c>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4081,15 +4081,19 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Krishaa</t>
+          <t>Elisabeth</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Makkar</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr"/>
+          <t>Bajet</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>eilbajet@gmail.com</t>
+        </is>
+      </c>
       <c r="D186" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4099,15 +4103,19 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Kunsh</t>
+          <t>Tailem</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Makkar</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr"/>
+          <t>Gingras</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>tag2005@icloud.com</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4117,17 +4125,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>jill</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Senecal</t>
+          <t>singleton</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>letournicoteur@gmail.com</t>
+          <t>guest.guest@gmail.com</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4139,15 +4147,19 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Giusmukh</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr"/>
+          <t>Blacker</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>blacker.shannon@gmail.com</t>
+        </is>
+      </c>
       <c r="D189" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4157,15 +4169,19 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Amandeep</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr"/>
+          <t>Furtado</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>sydneyfurtado06@gmail.com</t>
+        </is>
+      </c>
       <c r="D190" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4175,15 +4191,19 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Teghveer</t>
+          <t>Douglas</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr"/>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>hikeradk04@yahoo.com</t>
+        </is>
+      </c>
       <c r="D191" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4193,15 +4213,19 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Kaemanveer</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr"/>
+          <t>Perryman</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>sandyperryman59#1@gmail.com</t>
+        </is>
+      </c>
       <c r="D192" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4211,15 +4235,19 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Waring</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr"/>
+          <t>Beaudoin</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>laurenbeaudoin@hotmail.com</t>
+        </is>
+      </c>
       <c r="D193" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4229,12 +4257,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Idrees</t>
+          <t>Krishaa</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Bijabhai</t>
+          <t>Makkar</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4247,12 +4275,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ziyaad</t>
+          <t>Kunsh</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Bijabhai</t>
+          <t>Makkar</t>
         </is>
       </c>
       <c r="C195" t="inlineStr"/>
@@ -4265,17 +4293,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Pley</t>
+          <t>Senecal</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>mpley9800@gmail.com</t>
+          <t>letournicoteur@gmail.com</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -4287,19 +4315,15 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Giusmukh</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ameral</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>email1233@email.com</t>
-        </is>
-      </c>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4309,19 +4333,15 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Helen</t>
+          <t>Amandeep</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Contreras</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>helen@cartwheelcare.org</t>
-        </is>
-      </c>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4331,19 +4351,15 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Kyungjin</t>
+          <t>Teghveer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Peters</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>aw_peters@yahoo.com</t>
-        </is>
-      </c>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4353,19 +4369,15 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Kaemanveer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Havell</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>njhavell@gmail.com</t>
-        </is>
-      </c>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4375,19 +4387,15 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Agiannidis</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>mikee_911@hotmail.com</t>
-        </is>
-      </c>
+          <t>Waring</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4397,12 +4405,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Leeja</t>
+          <t>Idrees</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Hajak</t>
+          <t>Bijabhai</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4415,12 +4423,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Niyah</t>
+          <t>Ziyaad</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Hajak</t>
+          <t>Bijabhai</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4433,15 +4441,19 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>McCracken</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr"/>
+          <t>Pley</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>mpley9800@gmail.com</t>
+        </is>
+      </c>
       <c r="D204" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4451,15 +4463,19 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Gloria</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr"/>
+          <t>Ameral</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>email1233@email.com</t>
+        </is>
+      </c>
       <c r="D205" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4469,17 +4485,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Philip</t>
+          <t>Helen</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Bistretzan</t>
+          <t>Contreras</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>philip.bistretzan@gmail.com</t>
+          <t>helen@cartwheelcare.org</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4491,17 +4507,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Kyungjin</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Peters</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>jaysalexander78@gmail.com</t>
+          <t>aw_peters@yahoo.com</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4513,15 +4529,19 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Moogk</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr"/>
+          <t>Havell</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>njhavell@gmail.com</t>
+        </is>
+      </c>
       <c r="D208" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4531,17 +4551,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Morrison</t>
+          <t>Agiannidis</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>lmorrison@swuftpearlprocess.ca</t>
+          <t>mikee_911@hotmail.com</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4553,19 +4573,15 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Macel</t>
+          <t>Leeja</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Richard</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>marcelrichardrealtor@gmauil.com</t>
-        </is>
-      </c>
+          <t>Hajak</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4575,12 +4591,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Niyah</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Moogk</t>
+          <t>Hajak</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -4593,12 +4609,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>McCracken</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4611,12 +4627,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>AJ</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Gloria</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4629,15 +4645,19 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Philip</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Leonardo</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
+          <t>Bistretzan</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>philip.bistretzan@gmail.com</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4647,15 +4667,19 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Peyton</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Leonardo</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr"/>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>jaysalexander78@gmail.com</t>
+        </is>
+      </c>
       <c r="D215" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4665,12 +4689,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Sami</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Siddiqi</t>
+          <t>Moogk</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4683,15 +4707,19 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Finnley</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Tams</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr"/>
+          <t>Morrison</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>lmorrison@swuftpearlprocess.ca</t>
+        </is>
+      </c>
       <c r="D217" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4701,15 +4729,19 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Macel</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Parteno</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr"/>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>marcelrichardrealtor@gmauil.com</t>
+        </is>
+      </c>
       <c r="D218" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4719,12 +4751,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>parteno</t>
+          <t>Moogk</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4737,12 +4769,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Saifaan</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Siddiqi</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4755,12 +4787,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Winter</t>
+          <t>AJ</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Tams</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4773,12 +4805,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Alya</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4791,12 +4823,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Salman</t>
+          <t>Peyton</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -4809,12 +4841,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Amal</t>
+          <t>Sami</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Ahmad</t>
+          <t>Siddiqi</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4827,12 +4859,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Rumi</t>
+          <t>Finnley</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Rehan</t>
+          <t>Tams</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4845,12 +4877,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Azlan</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Ahmad</t>
+          <t>Parteno</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4863,19 +4895,15 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Hashim</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Vekar</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>hashim.vekar@gmail.com</t>
-        </is>
-      </c>
+          <t>parteno</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4885,12 +4913,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Nora</t>
+          <t>Saifaan</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Mondor</t>
+          <t>Siddiqi</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4903,12 +4931,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Camden</t>
+          <t>Winter</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Tams</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4921,12 +4949,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>MacKenzie</t>
+          <t>Alya</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Lennon</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4939,12 +4967,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Salman</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -4957,12 +4985,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>calla</t>
+          <t>Amal</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Tams</t>
+          <t>Ahmad</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -4975,19 +5003,15 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>james</t>
+          <t>Rumi</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>burger</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>jamesburger@gmail.com</t>
-        </is>
-      </c>
+          <t>Rehan</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4997,12 +5021,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Pierce</t>
+          <t>Azlan</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Trott</t>
+          <t>Ahmad</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -5015,15 +5039,19 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Josephine</t>
+          <t>Hashim</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Doan</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr"/>
+          <t>Vekar</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>hashim.vekar@gmail.com</t>
+        </is>
+      </c>
       <c r="D235" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5033,12 +5061,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Darren</t>
+          <t>Nora</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Mondor</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -5051,12 +5079,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Camden</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Ropp</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -5069,12 +5097,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Benson</t>
+          <t>MacKenzie</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Ropp</t>
+          <t>Lennon</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5087,12 +5115,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Jade</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Rosebruch</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -5105,12 +5133,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Paisley</t>
+          <t>calla</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Lobbezoo</t>
+          <t>Tams</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5123,20 +5151,1390 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>james</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Guiam</t>
+          <t>burger</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>mark.p.guiam@mpgsportsco.com</t>
+          <t>jamesburger@gmail.com</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Pierce</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Trott</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Josephine</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Doan</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>WAYNE</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>PANSEGRAU</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>wayne@topshelfarena.com</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Darren</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Galway</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Ropp</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Benson</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Ropp</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Jade</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Rosebruch</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Paisley</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Lobbezoo</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Summerr</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Baadani</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>summerbaad@gmail.com</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Juilen</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Hobani</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Jori</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Hobani</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Sarah</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Ives</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>saranives@gmail.com</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Drew</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Bigras</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>drewbigras@outlook.com</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Abeer</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Adaini</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Daniyah</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Anwar</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Eyob</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Gebregziabher</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>boyeyob@gmail.com</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Rajdeep</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Samra</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>samrar1945@gmail.com</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Rassel</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Padillo</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>padillorassel@rocketmail.com</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Ramzi</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Hobani</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>hobaniramzi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Renna</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Baadani</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>rennab883@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Yousef</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>ahmad</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>yousef.dayani22@gmail.com</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Layan</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Tayden</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Figueiredo</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>tayden.fig@gmail.com</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Jacob</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Bushnell</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>bushnelljacob24@gmail.com</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Xavier</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Inacio</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>xavierinacio27@gmail.com</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Morsink</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>lmorsink4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Brandon Scott</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Chow</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Nadine</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Sison</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>sisonmaranadine@gmail.com</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Angie</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>markangpost@gmail.com</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Jason</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Goodfellow</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>jason.chorney@gmail.com</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Dean</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>ethandean427@gmail.com</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Aiden</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>eatmeh2007@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Hailey</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>haileynguyen2012@gmail.com</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Sophie</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>sophienguyen1507@gmail.com</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Jasleen</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Hans</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>jhans20016@gmail.com</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Coghill</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>jcoghill1@outlook.com</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Curtis</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>curtisbabg99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>dave</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>serpa</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>simplymasonry@gmail.com</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Neal</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Bouwneester</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>neal.bouwmeester@gmail.com</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Tyson</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>tysongood103@gmail.com</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>graceebaby99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Cameryn</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Rocha</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>camerynrochaa4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>De Sousa</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>dannydsoccer@gmail.com</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Vincent</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Perri</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>vinnyp19@icloud.com</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Goldberg-Rogers</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>ryangoldbergrogers@gmail.com</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Curtis</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>curtisbaby99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Seda</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Ertabak</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>sedaertabak@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Ossman</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>aliossman1234@outlook.com</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>duong</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>nguyen</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>d.spam0707@gmail.com</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Khan</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>fatimak372@gmail.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Jibraan</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Salam</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>jibraan.salam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Kevin (Kerem)</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Ertabak</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>kevinertabak@gmail.com</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Ria</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Oanes</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>oaneslaw@gmail.com</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Caskie</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>jencaskie@gmail.com</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Dekort</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>jordandekort@gmail.com</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Don</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Oanes</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>kamonte311@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Abby</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>abby06green@gmail.com</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Caleb</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Garchinski</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>c13garch@gmail.com</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Enes</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Guneri</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>enesgg90@gmail.com</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Faizah</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Gaya</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>faizah.gaya@gmail.com</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Kimberly</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Saunders</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>kimlsaunders@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Brenda</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Tremblay</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>brentrem73@gmail.com</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Emilie</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Bilodeau</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>emiliebilodeauu@gmail.com</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Cambridge.xlsx
+++ b/docs/downloads/Cambridge.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D306"/>
+  <dimension ref="A1:D339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6540,6 +6540,724 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Luba</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Rodik</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>lubarudik@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Rod</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Fresnedi</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>rodfres26@gmail.com</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Fran</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>frankcook@mac.com</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Arvind</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>aks9ca@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>valandchris@rogers.com</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>sparkie_jones@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Ashu</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Khanna</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>sr71bb99@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Rita</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Khanna</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>rita.khanna18@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Katie</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Todd</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>katieajtodd@gmail.com</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Anil</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>a.nagpal@rogers.com</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Dana</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Ristic</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>ristic44@gmail.com</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Ross</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Mcgcoch</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>roscr17@live.ca</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Cohen</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Delvecchil</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>jam_delvecchil@gmail.com</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Mike</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Daly</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>mikeeee@rogers.com</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>janet</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>nolan</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>janetnolan6@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Riya</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>preeti</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>wadhwa</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>preetiwadhwa87@gmail.com</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Andrew</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>akcook@carolina.rr.com</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Anto</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>ranto1993@gmail.com</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Rob</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Grahn</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>robjobgrahn@outlook.com</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Riya</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Kevin</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Fernandes</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>all_temp@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Vikas</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Sakariya</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>sakariyavikas@gmail.com</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Lyka</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Fresnedi</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>lykafresnedi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Graeme</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>McMath</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>gtmcmath@gmail.com</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Seibold</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>fatimaseibold@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Denise</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Jones</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>denisejanetjones@gmail.com</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Neal</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Bouwneester</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>nbouwmeester@gmail.com</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Saurabh</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Chopra</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>schopra86@live.com</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Kristy</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>MacGregor</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>kristy.hallx@gmail.com</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Chu</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Tan</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>tan.chu1997@gmail.com</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Seibold</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>dale.seibold@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Seller</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>valandchris@roger.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/Cambridge.xlsx
+++ b/docs/downloads/Cambridge.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D339"/>
+  <dimension ref="A1:D401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -479,17 +479,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sherwin</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cruz</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sherwincruz297@gmail.com</t>
+          <t>nathan342@rogers.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -501,17 +501,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Bulmer</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nathan342@rogers.com</t>
+          <t>joshbulmer@live.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -523,17 +523,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bulmer</t>
+          <t>Truax</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>joshbulmer@live.com</t>
+          <t>dtruax72@gmail.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -545,17 +545,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Benoit</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Truax</t>
+          <t>Bourgault</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dtruax72@gmail.com</t>
+          <t>gotyourmessage@gmail.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,17 +567,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Benoit</t>
+          <t>Pauline</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bourgault</t>
+          <t>Szeto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>gotyourmessage@gmail.com</t>
+          <t>paulines_5@hotmail.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -589,17 +589,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pauline</t>
+          <t>Ramit</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Szeto</t>
+          <t>Raj</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>paulines_5@hotmail.com</t>
+          <t>ramit@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,17 +611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ramit</t>
+          <t>Audrie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Raj</t>
+          <t>Bouwmeester</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ramit@pickleplexclub.ca</t>
+          <t>audriebouwmeester@live.ca</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -633,17 +633,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Audrie</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bouwmeester</t>
+          <t>Ratcliff</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>audriebouwmeester@live.ca</t>
+          <t>andrew.ratcliff@rogers.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -655,17 +655,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Areeb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Waring</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tinalwaring@gmail.com</t>
+          <t>areebman@hotmail.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -677,17 +677,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Waring</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fc8833@yahoo.ca</t>
+          <t>tinalwaring@gmail.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -699,17 +699,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Milja</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gillespie</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>miljagillespie@gmail.com</t>
+          <t>fc8833@yahoo.ca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -721,17 +721,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Milja</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hannay</t>
+          <t>Gillespie</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>shannay@rogers.com</t>
+          <t>miljagillespie@gmail.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,17 +743,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Maddie</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Hannay</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>lena28ca@yahoo.com</t>
+          <t>shannay@rogers.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -765,17 +765,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Maddie</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Truax</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dltruax@rogers.com</t>
+          <t>lena28ca@yahoo.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -787,17 +787,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kesselring</t>
+          <t>Truax</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>timkesselring33@gmail.com</t>
+          <t>dltruax@rogers.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -809,17 +809,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Kesselring</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>phrednlare@hotmail.com</t>
+          <t>timkesselring33@gmail.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,17 +831,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Couch</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ajcouch2021@gmail.com</t>
+          <t>phrednlare@hotmail.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Katie</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kesselring</t>
+          <t>Couch</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>katiekesselring@gmail.com</t>
+          <t>ajcouch2021@gmail.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -875,17 +875,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kamil</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Machnik</t>
+          <t>Kesselring</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>kamil.machnik@hotmail.com</t>
+          <t>katiekesselring@gmail.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -897,17 +897,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rev</t>
+          <t>Kamil</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jayakumar</t>
+          <t>Machnik</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>revjk18@gmail.com</t>
+          <t>kamil.machnik@hotmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -919,17 +919,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Rev</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mercier</t>
+          <t>Jayakumar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dalemercier6193@gmail.com</t>
+          <t>revjk18@gmail.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -941,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Blair</t>
+          <t>Dale</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mcdonald</t>
+          <t>Mercier</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>blairmcdonald.ca@gmail.com</t>
+          <t>dalemercier6193@gmail.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bojan</t>
+          <t>Blair</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Batricevic</t>
+          <t>Mcdonald</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>bojanbatricevic@gmail.com</t>
+          <t>blairmcdonald.ca@gmail.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Asif</t>
+          <t>Bojan</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alidina</t>
+          <t>Batricevic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>asif+@pickleplexclub.ca</t>
+          <t>bojanbatricevic@gmail.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Asif</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Alidina</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ksbailey@yahoo.com</t>
+          <t>asif+@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1029,17 +1029,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bridgman</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>susan_bridge@live.ca</t>
+          <t>ksbailey@yahoo.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Siya</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sood</t>
+          <t>Bridgman</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>siyasood1107@gmail.com</t>
+          <t>susan_bridge@live.ca</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Siya</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Polzin</t>
+          <t>Sood</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>polzinlandscaping@me.com</t>
+          <t>siyasood1107@gmail.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rawn</t>
+          <t>Polzin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>brycerawn18@gmail.com</t>
+          <t>polzinlandscaping@me.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Csaszar</t>
+          <t>Rawn</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>matthewcsaszar@gmail.com</t>
+          <t>brycerawn18@gmail.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pat</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Grasso</t>
+          <t>Csaszar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>pat.grasso@togers.com</t>
+          <t>matthewcsaszar@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nghia</t>
+          <t>Pat</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Duong</t>
+          <t>Grasso</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nghiadduong@gmail.com</t>
+          <t>pat.grasso@togers.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Nghia</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sponder</t>
+          <t>Duong</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>chris.sponder@gmail.com</t>
+          <t>nghiadduong@gmail.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pickleplex</t>
+          <t>Sponder</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cambridge@pickleplexclub.ca</t>
+          <t>chris.sponder@gmail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bradshaw</t>
+          <t>Pickleplex</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>abradshaw435@gmail.com</t>
+          <t>cambridge@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Juniper</t>
+          <t>Bradshaw</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>maureen@praxispr.ca</t>
+          <t>abradshaw435@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Vince</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Alviano</t>
+          <t>Colanardi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>lisaa@rogers.com</t>
+          <t>vincevince2929@hotmail.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dean</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Juniper</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>deanjmac@yahoo.ca</t>
+          <t>maureen@praxispr.ca</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Alviano</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jay@pickleplexclub.ca</t>
+          <t>lisaa@rogers.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Yong</t>
+          <t>Dean</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>yon_liu@hotmail.com</t>
+          <t>deanjmac@yahoo.ca</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Leiskau</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kara@jdgraphics.com</t>
+          <t>jay@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,15 +1381,19 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Devanshi</t>
+          <t>Yong</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Mistry</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>yon_liu@hotmail.com</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1399,15 +1403,19 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Beckett</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>Leiskau</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>kara@jdgraphics.com</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1417,12 +1425,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Devanshi</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Mistry</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1435,12 +1443,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Amaya</t>
+          <t>Beckett</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ismail</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1453,12 +1461,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Paige</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pilkey</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1471,12 +1479,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Finnley</t>
+          <t>Amaya</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Ismail</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1489,7 +1497,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Paige</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1507,7 +1515,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Marigold</t>
+          <t>Finnley</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1525,12 +1533,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kollar</t>
+          <t>Pilkey</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1543,12 +1551,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Kavir</t>
+          <t>Marigold</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1561,12 +1569,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pilkey</t>
+          <t>Kollar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1579,12 +1587,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Anise</t>
+          <t>Kavir</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ismail</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1597,12 +1605,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Silas</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pharoah</t>
+          <t>Pilkey</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1615,19 +1623,15 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hilda</t>
+          <t>Anise</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dusek</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>mhdudek@gmail.com</t>
-        </is>
-      </c>
+          <t>Ismail</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1637,7 +1641,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Verne</t>
+          <t>Silas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1655,15 +1659,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Hilda</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Souza Cefrin da Silva</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Dusek</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>mhdudek@gmail.com</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1673,12 +1681,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Wesley</t>
+          <t>Verne</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Yuricek</t>
+          <t>Pharoah</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1691,12 +1699,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sayali</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Parkhi</t>
+          <t>Souza Cefrin da Silva</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1709,12 +1717,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Gabby</t>
+          <t>Wesley</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Yuricek</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1727,12 +1735,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Sayali</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>Parkhi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1745,12 +1753,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Rhonda</t>
+          <t>Gabby</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kalverda</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1763,12 +1771,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Reagan</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1781,12 +1789,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Rhonda</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>Kalverda</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1799,12 +1807,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Reagan</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Yuricek</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1817,12 +1825,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Devan</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bhatt</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1835,12 +1843,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>Yuricek</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1853,12 +1861,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Devan</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stead</t>
+          <t>Bhatt</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1871,12 +1879,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>brian</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Hicks</t>
+          <t>le</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1889,12 +1897,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Armen</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kabakian</t>
+          <t>Stead</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1907,12 +1915,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kaiya</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>Hicks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1925,12 +1933,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Greyson</t>
+          <t>Armen</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>Kabakian</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1943,7 +1951,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Kaiya</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1961,12 +1969,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Greyson</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ottman</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1979,12 +1987,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Grayson</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Taneza</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1997,12 +2005,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Ottman</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2015,12 +2023,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Grayson</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Taneza</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2033,12 +2041,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Valeria</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mencia</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2051,19 +2059,15 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>De almeida</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>daniel.abeldealmeida@gmail.com</t>
-        </is>
-      </c>
+          <t>Baxter</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2073,12 +2077,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Valeria</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jauregui</t>
+          <t>Mencia</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2091,15 +2095,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dandrea</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>De almeida</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>daniel.abeldealmeida@gmail.com</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2109,12 +2117,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Cesar</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Diaz</t>
+          <t>Jauregui</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2127,12 +2135,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ripley</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Matheson</t>
+          <t>Dandrea</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2145,19 +2153,15 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Jean-paul</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Morgan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>morganjea18@gmail.com</t>
-        </is>
-      </c>
+          <t>Diaz</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2167,12 +2171,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>POOJA</t>
+          <t>Ripley</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pawar</t>
+          <t>Matheson</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2185,15 +2189,19 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Neel</t>
+          <t>Jean-paul</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Gondalia</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>Morgan</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>morganjea18@gmail.com</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2203,12 +2211,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>POOJA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sharp</t>
+          <t>Pawar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2221,12 +2229,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Gondalia</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2239,12 +2247,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Duong</t>
+          <t>Sharp</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2257,12 +2265,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2275,12 +2283,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Clara</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Duong</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2293,12 +2301,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Maxwell</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Mondor</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2311,12 +2319,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Clara</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>McDonald</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2329,19 +2337,15 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Maxwell</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>5116rpb@gmail.com</t>
-        </is>
-      </c>
+          <t>Mondor</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2351,12 +2355,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Beck</t>
+          <t>McDonald</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2369,15 +2373,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Nora</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Mondor</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>5116rpb@gmail.com</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2387,12 +2395,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Payton</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Marr</t>
+          <t>Beck</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2405,12 +2413,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Raphael</t>
+          <t>Nora</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
+          <t>Mondor</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2423,19 +2431,15 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Payton</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>rplayer.4050@gmail.com</t>
-        </is>
-      </c>
+          <t>Marr</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2445,12 +2449,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Raphael</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Coelho</t>
+          <t>Del Rosario</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2463,17 +2467,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Will</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Law</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>solis.environmental@gmail.com</t>
+          <t>rplayer.4050@gmail.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -2485,7 +2489,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2503,15 +2507,19 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>Law</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>solis.environmental@gmail.com</t>
+        </is>
+      </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2521,7 +2529,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2539,12 +2547,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2557,12 +2565,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2575,12 +2583,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ballard</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2593,12 +2601,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Prachi</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>King</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2611,12 +2619,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Rolleman</t>
+          <t>Ballard</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2629,12 +2637,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Prachi</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2647,12 +2655,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Katrina</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>Rolleman</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2665,12 +2673,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Elissa</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>King</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2683,12 +2691,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Suzy</t>
+          <t>Katrina</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2701,12 +2709,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Elissa</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Huo</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2719,12 +2727,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Suzy</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2737,12 +2745,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Snook</t>
+          <t>Huo</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2755,12 +2763,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Jobathan</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Huo</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2773,12 +2781,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Snook</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2791,7 +2799,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Jobathan</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2809,7 +2817,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2827,12 +2835,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fry</t>
+          <t>Huo</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2845,12 +2853,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Lannutti</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2863,19 +2871,15 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Jasper</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Viado</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>jasper@pickleplexclub.ca</t>
-        </is>
-      </c>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2885,12 +2889,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Huehn</t>
+          <t>Lannutti</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2903,17 +2907,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Dhuha</t>
+          <t>Jasper</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Chaudhry</t>
+          <t>Viado</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>dhuha123@live.ca</t>
+          <t>jasper@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2925,7 +2929,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Declan</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -2943,15 +2947,19 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Lacey</t>
+          <t>Dhuha</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Huehn</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr"/>
+          <t>Chaudhry</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>dhuha123@live.ca</t>
+        </is>
+      </c>
       <c r="D129" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2961,12 +2969,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Declan</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ritchie</t>
+          <t>Huehn</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2979,12 +2987,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Lacey</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Ritchie</t>
+          <t>Huehn</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2997,19 +3005,15 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Morgan</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Mcallister</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>josh027girl@gmail.com</t>
-        </is>
-      </c>
+          <t>Ritchie</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3019,12 +3023,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Hardy</t>
+          <t>Ritchie</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3037,15 +3041,19 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Morgan</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>An</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>Mcallister</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>josh027girl@gmail.com</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3055,12 +3063,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Hardy</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3073,12 +3081,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Eliot</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>An</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3091,12 +3099,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Elliott</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Hardy</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3109,12 +3117,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Eliot</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kerr</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3127,19 +3135,15 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Elliott</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Amaral</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>jameralc522@rogers.com</t>
-        </is>
-      </c>
+          <t>Hardy</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3149,19 +3153,15 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Kharodia</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>zohra_kharodia@hotmail.com</t>
-        </is>
-      </c>
+          <t>Kerr</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3171,15 +3171,19 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Joe</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Kerr</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
+          <t>Amaral</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>jameralc522@rogers.com</t>
+        </is>
+      </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3189,17 +3193,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sandhu</t>
+          <t>Kharodia</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>jay@registon.ca</t>
+          <t>zohra_kharodia@hotmail.com</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -3211,19 +3215,15 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sheila</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Anonuevo</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>sheila.anonuevo@gmail.com</t>
-        </is>
-      </c>
+          <t>Kerr</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3233,17 +3233,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Sandhu</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>guest123$@hotmail.com</t>
+          <t>jay@registon.ca</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -3255,17 +3255,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Mufaddal</t>
+          <t>Sheila</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Jerwalla</t>
+          <t>Anonuevo</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>mufaddaljerwalla@gmail.com</t>
+          <t>sheila.anonuevo@gmail.com</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3277,15 +3277,19 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Guest</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr"/>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>guest123$@hotmail.com</t>
+        </is>
+      </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3295,15 +3299,19 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Grady</t>
+          <t>Mufaddal</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>More</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr"/>
+          <t>Jerwalla</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>mufaddaljerwalla@gmail.com</t>
+        </is>
+      </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3313,19 +3321,15 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Caroleann</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Fleming</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>carbyckshank@bell.net</t>
-        </is>
-      </c>
+          <t>Stewart</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3335,12 +3339,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Gwen</t>
+          <t>Grady</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dias</t>
+          <t>More</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3353,15 +3357,19 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Jaxon</t>
+          <t>Caroleann</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Vacon</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr"/>
+          <t>Fleming</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>carbyckshank@bell.net</t>
+        </is>
+      </c>
       <c r="D150" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3371,19 +3379,15 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Gwen</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Phan</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>phanmyster@gmail.com</t>
-        </is>
-      </c>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3393,19 +3397,15 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Elie</t>
+          <t>Jaxon</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Daccache</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>d.elie@ymail.com</t>
-        </is>
-      </c>
+          <t>Vacon</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3415,15 +3415,19 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Ferguson</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>Phan</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>phanmyster@gmail.com</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3433,15 +3437,19 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Elie</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Reiber</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr"/>
+          <t>Daccache</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>d.elie@ymail.com</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3451,12 +3459,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Sayavong</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3469,19 +3477,15 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Thirtle</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>sthirtle@rogers.com</t>
-        </is>
-      </c>
+          <t>Reiber</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3491,12 +3495,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Lockner</t>
+          <t>Sayavong</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3509,15 +3513,19 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Milo</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Moodley</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
+          <t>Thirtle</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>sthirtle@rogers.com</t>
+        </is>
+      </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3527,19 +3535,15 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Walls</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>abbydeane05@icloud.com</t>
-        </is>
-      </c>
+          <t>Lockner</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3549,19 +3553,15 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Milo</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Walls</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>shanny.deane@gmail.com</t>
-        </is>
-      </c>
+          <t>Moodley</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3571,17 +3571,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Nafisa</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Unia</t>
+          <t>Walls</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>nafisaunia1971@gmail.com</t>
+          <t>abbydeane05@icloud.com</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -3593,17 +3593,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Elsden</t>
+          <t>Walls</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>maxelsden@gmail.com</t>
+          <t>shanny.deane@gmail.com</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3615,17 +3615,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Nafisa</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Cymbalski</t>
+          <t>Unia</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>john.cymbalski@gmail.com</t>
+          <t>nafisaunia1971@gmail.com</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -3637,17 +3637,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Dawe</t>
+          <t>Elsden</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>rtdawe@icloud.com</t>
+          <t>maxelsden@gmail.com</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3659,17 +3659,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Arul</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Kumar</t>
+          <t>Cymbalski</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>dinsboyjr@gmail.com</t>
+          <t>john.cymbalski@gmail.com</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3681,17 +3681,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Vedansh</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Kokra</t>
+          <t>Dawe</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>vedansh.kokra@icloud.com</t>
+          <t>rtdawe@icloud.com</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3703,17 +3703,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>elisabeth</t>
+          <t>Arul</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>eden</t>
+          <t>Kumar</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>elisabeth.eden12@gmail.com</t>
+          <t>dinsboyjr@gmail.com</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3725,17 +3725,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Vedansh</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Genovese</t>
+          <t>Kokra</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>genoveseron9@gmail.com</t>
+          <t>vedansh.kokra@icloud.com</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3747,17 +3747,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Zachary</t>
+          <t>elisabeth</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Janzen</t>
+          <t>eden</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>zacharyj115@gmail.com</t>
+          <t>elisabeth.eden12@gmail.com</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -3769,17 +3769,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Mabel</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Dawe</t>
+          <t>Genovese</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>mabeldawe@msn.com</t>
+          <t>genoveseron9@gmail.com</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3791,17 +3791,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>Zachary</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Shah</t>
+          <t>Janzen</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>advaitshah323@gmail.com</t>
+          <t>zacharyj115@gmail.com</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3813,17 +3813,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Connie</t>
+          <t>Mabel</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Parsons</t>
+          <t>Dawe</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>david.parsons4@sympatico.ca</t>
+          <t>mabeldawe@msn.com</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3835,17 +3835,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Yang - t</t>
+          <t>Shah</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>yang.julie519@trial.ca</t>
+          <t>advaitshah323@gmail.com</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3857,17 +3857,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Connie</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Maier</t>
+          <t>Parsons</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>shannonmaier@gmail.com</t>
+          <t>david.parsons4@sympatico.ca</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3879,17 +3879,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Awakian</t>
+          <t>Yang - t</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>jack@tricityflooring.ca</t>
+          <t>yang.julie519@trial.ca</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3901,15 +3901,19 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Macy</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr"/>
+          <t>Maier</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>shannonmaier@gmail.com</t>
+        </is>
+      </c>
       <c r="D176" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3919,15 +3923,19 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Ainsworth</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr"/>
+          <t>Awakian</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>jack@tricityflooring.ca</t>
+        </is>
+      </c>
       <c r="D177" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3937,7 +3945,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Ainsley</t>
+          <t>Macy</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3955,12 +3963,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Inaya</t>
+          <t>Ainsworth</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Sajid</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -3973,12 +3981,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Zayan</t>
+          <t>Ainsley</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Sajid</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -3991,12 +3999,12 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Giselle</t>
+          <t>Inaya</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
+          <t>Sajid</t>
         </is>
       </c>
       <c r="C181" t="inlineStr"/>
@@ -4009,12 +4017,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Zayan</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Waring</t>
+          <t>Sajid</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4027,12 +4035,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Giselle</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Del Rosario</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4045,12 +4053,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Rian</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Waring</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4063,7 +4071,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Tesia</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4081,19 +4089,15 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Elisabeth</t>
+          <t>Rian</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Bajet</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>eilbajet@gmail.com</t>
-        </is>
-      </c>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4103,19 +4107,15 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Tailem</t>
+          <t>Tesia</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Gingras</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>tag2005@icloud.com</t>
-        </is>
-      </c>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4125,17 +4125,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>jill</t>
+          <t>Elisabeth</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>singleton</t>
+          <t>Bajet</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>guest.guest@gmail.com</t>
+          <t>eilbajet@gmail.com</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4147,17 +4147,17 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Tailem</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Blacker</t>
+          <t>Gingras</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>blacker.shannon@gmail.com</t>
+          <t>tag2005@icloud.com</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4169,17 +4169,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>jill</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Furtado</t>
+          <t>singleton</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>sydneyfurtado06@gmail.com</t>
+          <t>guest.guest@gmail.com</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4191,17 +4191,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Bauer</t>
+          <t>Blacker</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>hikeradk04@yahoo.com</t>
+          <t>blacker.shannon@gmail.com</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -4213,17 +4213,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Perryman</t>
+          <t>Furtado</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>sandyperryman59#1@gmail.com</t>
+          <t>sydneyfurtado06@gmail.com</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4235,17 +4235,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Douglas</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Beaudoin</t>
+          <t>Bauer</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>laurenbeaudoin@hotmail.com</t>
+          <t>hikeradk04@yahoo.com</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4257,15 +4257,19 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Krishaa</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Makkar</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr"/>
+          <t>Perryman</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>sandyperryman59#1@gmail.com</t>
+        </is>
+      </c>
       <c r="D194" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4275,15 +4279,19 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Kunsh</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Makkar</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
+          <t>Beaudoin</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>laurenbeaudoin@hotmail.com</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4293,19 +4301,15 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Krishaa</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Senecal</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>letournicoteur@gmail.com</t>
-        </is>
-      </c>
+          <t>Makkar</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4315,12 +4319,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Giusmukh</t>
+          <t>Kunsh</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Makkar</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4333,15 +4337,19 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Amandeep</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr"/>
+          <t>Senecal</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>letournicoteur@gmail.com</t>
+        </is>
+      </c>
       <c r="D198" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4351,7 +4359,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Teghveer</t>
+          <t>Giusmukh</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4369,7 +4377,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Kaemanveer</t>
+          <t>Amandeep</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4387,12 +4395,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Teghveer</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Waring</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4405,12 +4413,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Idrees</t>
+          <t>Kaemanveer</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Bijabhai</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4423,12 +4431,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Ziyaad</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Bijabhai</t>
+          <t>Waring</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4441,19 +4449,15 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Idrees</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Pley</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>mpley9800@gmail.com</t>
-        </is>
-      </c>
+          <t>Bijabhai</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4463,19 +4467,15 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Ziyaad</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Ameral</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>email1233@email.com</t>
-        </is>
-      </c>
+          <t>Bijabhai</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4485,17 +4485,17 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Helen</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Contreras</t>
+          <t>Pley</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>helen@cartwheelcare.org</t>
+          <t>mpley9800@gmail.com</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -4507,17 +4507,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Kyungjin</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Peters</t>
+          <t>Ameral</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>aw_peters@yahoo.com</t>
+          <t>email1233@email.com</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4529,17 +4529,17 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Helen</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Havell</t>
+          <t>Contreras</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>njhavell@gmail.com</t>
+          <t>helen@cartwheelcare.org</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -4551,17 +4551,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Kyungjin</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Agiannidis</t>
+          <t>Peters</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>mikee_911@hotmail.com</t>
+          <t>aw_peters@yahoo.com</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -4573,15 +4573,19 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Leeja</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Hajak</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr"/>
+          <t>Havell</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>njhavell@gmail.com</t>
+        </is>
+      </c>
       <c r="D210" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4591,15 +4595,19 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Niyah</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Hajak</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
+          <t>Agiannidis</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>mikee_911@hotmail.com</t>
+        </is>
+      </c>
       <c r="D211" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4609,12 +4617,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Leeja</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>McCracken</t>
+          <t>Hajak</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4627,12 +4635,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Niyah</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Gloria</t>
+          <t>Hajak</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4645,19 +4653,15 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Philip</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Bistretzan</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>philip.bistretzan@gmail.com</t>
-        </is>
-      </c>
+          <t>McCracken</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4667,19 +4671,15 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Alexander</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>jaysalexander78@gmail.com</t>
-        </is>
-      </c>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4689,15 +4689,19 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Philip</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Moogk</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr"/>
+          <t>Bistretzan</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>philip.bistretzan@gmail.com</t>
+        </is>
+      </c>
       <c r="D216" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4707,17 +4711,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Morrison</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>lmorrison@swuftpearlprocess.ca</t>
+          <t>jaysalexander78@gmail.com</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -4729,19 +4733,15 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Macel</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Richard</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>marcelrichardrealtor@gmauil.com</t>
-        </is>
-      </c>
+          <t>Moogk</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4751,15 +4751,19 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Moogk</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr"/>
+          <t>Morrison</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>lmorrison@swuftpearlprocess.ca</t>
+        </is>
+      </c>
       <c r="D219" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4769,15 +4773,19 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Macel</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Leonardo</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr"/>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>marcelrichardrealtor@gmauil.com</t>
+        </is>
+      </c>
       <c r="D220" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4787,12 +4795,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>AJ</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Moogk</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4805,7 +4813,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4823,7 +4831,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Peyton</t>
+          <t>AJ</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -4841,12 +4849,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Sami</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Siddiqi</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4859,12 +4867,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Finnley</t>
+          <t>Peyton</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Tams</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4877,12 +4885,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Sami</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Parteno</t>
+          <t>Siddiqi</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4895,12 +4903,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Finnley</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>parteno</t>
+          <t>Tams</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4913,12 +4921,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Saifaan</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Siddiqi</t>
+          <t>Parteno</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4931,12 +4939,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Winter</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Tams</t>
+          <t>parteno</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4949,12 +4957,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Alya</t>
+          <t>Saifaan</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Siddiqi</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4967,12 +4975,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Salman</t>
+          <t>Winter</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Tams</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -4985,12 +4993,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Amal</t>
+          <t>Alya</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Ahmad</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -5003,12 +5011,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Rumi</t>
+          <t>Salman</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Rehan</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -5021,7 +5029,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Azlan</t>
+          <t>Amal</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5039,19 +5047,15 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Hashim</t>
+          <t>Rumi</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Vekar</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>hashim.vekar@gmail.com</t>
-        </is>
-      </c>
+          <t>Rehan</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5061,12 +5065,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Nora</t>
+          <t>Azlan</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Mondor</t>
+          <t>Ahmad</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -5079,15 +5083,19 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Camden</t>
+          <t>Hashim</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Koch</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr"/>
+          <t>Vekar</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>hashim.vekar@gmail.com</t>
+        </is>
+      </c>
       <c r="D237" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5097,12 +5105,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>MacKenzie</t>
+          <t>Nora</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Lennon</t>
+          <t>Mondor</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5115,7 +5123,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Camden</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5133,12 +5141,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>calla</t>
+          <t>MacKenzie</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Tams</t>
+          <t>Lennon</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5151,19 +5159,15 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>james</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>burger</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>jamesburger@gmail.com</t>
-        </is>
-      </c>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5173,12 +5177,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Pierce</t>
+          <t>calla</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Trott</t>
+          <t>Tams</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5191,15 +5195,19 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Josephine</t>
+          <t>james</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Doan</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
+          <t>burger</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>jamesburger@gmail.com</t>
+        </is>
+      </c>
       <c r="D243" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5209,19 +5217,15 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>WAYNE</t>
+          <t>Pierce</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PANSEGRAU</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>wayne@topshelfarena.com</t>
-        </is>
-      </c>
+          <t>Trott</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5231,12 +5235,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Darren</t>
+          <t>Josephine</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Doan</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5249,15 +5253,19 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>WAYNE</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Ropp</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr"/>
+          <t>PANSEGRAU</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>wayne@topshelfarena.com</t>
+        </is>
+      </c>
       <c r="D246" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5267,12 +5275,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Benson</t>
+          <t>Darren</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Ropp</t>
+          <t>Galway</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5285,12 +5293,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Jade</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Rosebruch</t>
+          <t>Ropp</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5303,12 +5311,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Paisley</t>
+          <t>Benson</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Lobbezoo</t>
+          <t>Ropp</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -5321,19 +5329,15 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Summerr</t>
+          <t>Jade</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Baadani</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>summerbaad@gmail.com</t>
-        </is>
-      </c>
+          <t>Rosebruch</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5343,12 +5347,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Juilen</t>
+          <t>Paisley</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Hobani</t>
+          <t>Lobbezoo</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5361,15 +5365,19 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Jori</t>
+          <t>Summerr</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Hobani</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr"/>
+          <t>Baadani</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>summerbaad@gmail.com</t>
+        </is>
+      </c>
       <c r="D252" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5379,19 +5387,15 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Juilen</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Ives</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>saranives@gmail.com</t>
-        </is>
-      </c>
+          <t>Hobani</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5401,19 +5405,15 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Jori</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Bigras</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>drewbigras@outlook.com</t>
-        </is>
-      </c>
+          <t>Hobani</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5423,15 +5423,19 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Abeer</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Adaini</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr"/>
+          <t>Ives</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>saranives@gmail.com</t>
+        </is>
+      </c>
       <c r="D255" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5441,15 +5445,19 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Daniyah</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Ahmad</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr"/>
+          <t>Bigras</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>drewbigras@outlook.com</t>
+        </is>
+      </c>
       <c r="D256" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5459,12 +5467,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Anwar</t>
+          <t>Abeer</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Ahmad</t>
+          <t>Adaini</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5477,19 +5485,15 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Eyob</t>
+          <t>Daniyah</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Gebregziabher</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>boyeyob@gmail.com</t>
-        </is>
-      </c>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5499,19 +5503,15 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Rajdeep</t>
+          <t>Anwar</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Samra</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>samrar1945@gmail.com</t>
-        </is>
-      </c>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5521,17 +5521,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Rassel</t>
+          <t>Eyob</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Padillo</t>
+          <t>Gebregziabher</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>padillorassel@rocketmail.com</t>
+          <t>boyeyob@gmail.com</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -5543,17 +5543,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Ramzi</t>
+          <t>Rajdeep</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Hobani</t>
+          <t>Samra</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>hobaniramzi@gmail.com</t>
+          <t>samrar1945@gmail.com</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -5565,17 +5565,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Rassel</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Baadani</t>
+          <t>Padillo</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>rennab883@yahoo.com</t>
+          <t>padillorassel@rocketmail.com</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -5587,17 +5587,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Yousef</t>
+          <t>Ramzi</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>ahmad</t>
+          <t>Hobani</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>yousef.dayani22@gmail.com</t>
+          <t>hobaniramzi@gmail.com</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -5609,15 +5609,19 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Layan</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Ahmad</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr"/>
+          <t>Baadani</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>rennab883@yahoo.com</t>
+        </is>
+      </c>
       <c r="D264" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5627,17 +5631,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Tayden</t>
+          <t>Yousef</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Figueiredo</t>
+          <t>ahmad</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>tayden.fig@gmail.com</t>
+          <t>yousef.dayani22@gmail.com</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -5649,19 +5653,15 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Layan</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Bushnell</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>bushnelljacob24@gmail.com</t>
-        </is>
-      </c>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5671,17 +5671,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Tayden</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Inacio</t>
+          <t>Figueiredo</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>xavierinacio27@gmail.com</t>
+          <t>tayden.fig@gmail.com</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -5693,17 +5693,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Morsink</t>
+          <t>Bushnell</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>lmorsink4@gmail.com</t>
+          <t>bushnelljacob24@gmail.com</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -5715,15 +5715,19 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Wang</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr"/>
+          <t>Inacio</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>xavierinacio27@gmail.com</t>
+        </is>
+      </c>
       <c r="D269" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5733,15 +5737,19 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Brandon Scott</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Chow</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr"/>
+          <t>Morsink</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>lmorsink4@gmail.com</t>
+        </is>
+      </c>
       <c r="D270" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5751,19 +5759,15 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Nadine</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Sison</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>sisonmaranadine@gmail.com</t>
-        </is>
-      </c>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr"/>
       <c r="D271" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5773,19 +5777,15 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Angie</t>
+          <t>Brandon Scott</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Post</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>markangpost@gmail.com</t>
-        </is>
-      </c>
+          <t>Chow</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5795,17 +5795,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Nadine</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Goodfellow</t>
+          <t>Sison</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>jason.chorney@gmail.com</t>
+          <t>sisonmaranadine@gmail.com</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -5817,17 +5817,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Angie</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Dean</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>ethandean427@gmail.com</t>
+          <t>markangpost@gmail.com</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -5839,17 +5839,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Goodfellow</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>eatmeh2007@yahoo.com</t>
+          <t>jason.chorney@gmail.com</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -5861,17 +5861,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Dean</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>haileynguyen2012@gmail.com</t>
+          <t>ethandean427@gmail.com</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -5883,7 +5883,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Sophie</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>sophienguyen1507@gmail.com</t>
+          <t>eatmeh2007@yahoo.com</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -5905,17 +5905,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Jasleen</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Hans</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>jhans20016@gmail.com</t>
+          <t>haileynguyen2012@gmail.com</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -5927,17 +5927,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Sophie</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Coghill</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>jcoghill1@outlook.com</t>
+          <t>sophienguyen1507@gmail.com</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -5949,17 +5949,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Jasleen</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Hans</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>curtisbabg99@gmail.com</t>
+          <t>jhans20016@gmail.com</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -5971,17 +5971,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>dave</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>serpa</t>
+          <t>Coghill</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>simplymasonry@gmail.com</t>
+          <t>jcoghill1@outlook.com</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -5993,17 +5993,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Neal</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Bouwneester</t>
+          <t>Baby</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>neal.bouwmeester@gmail.com</t>
+          <t>curtisbabg99@gmail.com</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6015,17 +6015,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Tyson</t>
+          <t>dave</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>serpa</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>tysongood103@gmail.com</t>
+          <t>simplymasonry@gmail.com</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6037,17 +6037,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Neal</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Bouwneester</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>graceebaby99@gmail.com</t>
+          <t>neal.bouwmeester@gmail.com</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6059,17 +6059,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Cameryn</t>
+          <t>Tyson</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Rocha</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>camerynrochaa4@gmail.com</t>
+          <t>tysongood103@gmail.com</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6081,17 +6081,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>De Sousa</t>
+          <t>Baby</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>dannydsoccer@gmail.com</t>
+          <t>graceebaby99@gmail.com</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6103,17 +6103,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Cameryn</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Perri</t>
+          <t>Rocha</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>vinnyp19@icloud.com</t>
+          <t>camerynrochaa4@gmail.com</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -6125,17 +6125,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Goldberg-Rogers</t>
+          <t>De Sousa</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>ryangoldbergrogers@gmail.com</t>
+          <t>dannydsoccer@gmail.com</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6147,17 +6147,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Perri</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>curtisbaby99@gmail.com</t>
+          <t>vinnyp19@icloud.com</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6169,17 +6169,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Seda</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Ertabak</t>
+          <t>Goldberg-Rogers</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>sedaertabak@hotmail.com</t>
+          <t>ryangoldbergrogers@gmail.com</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6191,17 +6191,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Ossman</t>
+          <t>Baby</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>aliossman1234@outlook.com</t>
+          <t>curtisbaby99@gmail.com</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6213,17 +6213,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>duong</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>nguyen</t>
+          <t>Ertabak</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>d.spam0707@gmail.com</t>
+          <t>sedaertabak@hotmail.com</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6235,17 +6235,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Ossman</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>fatimak372@gmail.com</t>
+          <t>aliossman1234@outlook.com</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6257,17 +6257,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Jibraan</t>
+          <t>duong</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Salam</t>
+          <t>nguyen</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>jibraan.salam@gmail.com</t>
+          <t>d.spam0707@gmail.com</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6279,17 +6279,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Kevin (Kerem)</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Ertabak</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>kevinertabak@gmail.com</t>
+          <t>fatimak372@gmail.com</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6301,17 +6301,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Ria</t>
+          <t>Jibraan</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Oanes</t>
+          <t>Salam</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>oaneslaw@gmail.com</t>
+          <t>jibraan.salam@gmail.com</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6323,17 +6323,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Kevin (Kerem)</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Caskie</t>
+          <t>Ertabak</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>jencaskie@gmail.com</t>
+          <t>kevinertabak@gmail.com</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6345,17 +6345,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Ria</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Dekort</t>
+          <t>Oanes</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>jordandekort@gmail.com</t>
+          <t>oaneslaw@gmail.com</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6367,17 +6367,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Don</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Oanes</t>
+          <t>Caskie</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>kamonte311@yahoo.com</t>
+          <t>jencaskie@gmail.com</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -6389,17 +6389,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Dekort</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>abby06green@gmail.com</t>
+          <t>jordandekort@gmail.com</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -6411,17 +6411,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Caleb</t>
+          <t>Don</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Garchinski</t>
+          <t>Oanes</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>c13garch@gmail.com</t>
+          <t>kamonte311@yahoo.com</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -6433,17 +6433,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Enes</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Guneri</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>enesgg90@gmail.com</t>
+          <t>abby06green@gmail.com</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -6455,17 +6455,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Faizah</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Gaya</t>
+          <t>Garchinski</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>faizah.gaya@gmail.com</t>
+          <t>c13garch@gmail.com</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -6477,17 +6477,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Kimberly</t>
+          <t>Enes</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Saunders</t>
+          <t>Guneri</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>kimlsaunders@yahoo.ca</t>
+          <t>enesgg90@gmail.com</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -6499,17 +6499,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>Faizah</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Tremblay</t>
+          <t>Gaya</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>brentrem73@gmail.com</t>
+          <t>faizah.gaya@gmail.com</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -6521,17 +6521,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Kimberly</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Bilodeau</t>
+          <t>Saunders</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>emiliebilodeauu@gmail.com</t>
+          <t>kimlsaunders@yahoo.ca</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -6543,17 +6543,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Luba</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Rodik</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>lubarudik@yahoo.com</t>
+          <t>brentrem73@gmail.com</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -6565,17 +6565,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Rod</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Fresnedi</t>
+          <t>Bilodeau</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>rodfres26@gmail.com</t>
+          <t>emiliebilodeauu@gmail.com</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -6587,17 +6587,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Fran</t>
+          <t>Luba</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Rudik</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>frankcook@mac.com</t>
+          <t>lubarudik@yahoo.com</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -6609,17 +6609,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Arvind</t>
+          <t>Neschelle</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Prame</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>aks9ca@yahoo.com</t>
+          <t>neschellelok@yahoo.ca</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -6631,17 +6631,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Val</t>
+          <t>Rod</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>valandchris@rogers.com</t>
+          <t>rodfres26@gmail.com</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -6653,17 +6653,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Fran</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>sparkie_jones@hotmail.com</t>
+          <t>frankcook@mac.com</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -6675,17 +6675,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Ashu</t>
+          <t>Arvind</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Khanna</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>sr71bb99@yahoo.com</t>
+          <t>aks9ca@yahoo.com</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -6697,17 +6697,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Khanna</t>
+          <t>Seller</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>rita.khanna18@yahoo.ca</t>
+          <t>valandchris@rogers.com</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -6719,17 +6719,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Katie</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Todd</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>katieajtodd@gmail.com</t>
+          <t>sparkie_jones@hotmail.com</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -6741,17 +6741,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Anil</t>
+          <t>Ashu</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Nagpal</t>
+          <t>Khanna</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>a.nagpal@rogers.com</t>
+          <t>sr71bb99@yahoo.com</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -6763,17 +6763,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Ristic</t>
+          <t>Khanna</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>ristic44@gmail.com</t>
+          <t>rita.khanna18@yahoo.ca</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -6785,17 +6785,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Mcgcoch</t>
+          <t>Todd</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>roscr17@live.ca</t>
+          <t>katieajtodd@gmail.com</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -6807,17 +6807,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Cohen</t>
+          <t>Anil</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Delvecchil</t>
+          <t>Nagpal</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>jam_delvecchil@gmail.com</t>
+          <t>a.nagpal@rogers.com</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -6829,17 +6829,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Daly</t>
+          <t>Ristic</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>mikeeee@rogers.com</t>
+          <t>ristic44@gmail.com</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -6851,17 +6851,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>janet</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>nolan</t>
+          <t>Mcgcoch</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>janetnolan6@hotmail.com</t>
+          <t>roscr17@live.ca</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -6873,15 +6873,19 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Riya</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Nagpal</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr"/>
+          <t>Delvecchil</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>jam_delvecchil@gmail.com</t>
+        </is>
+      </c>
       <c r="D322" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -6891,17 +6895,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>preeti</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>wadhwa</t>
+          <t>Daly</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>preetiwadhwa87@gmail.com</t>
+          <t>mikeeee@rogers.com</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -6913,17 +6917,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>janet</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>nolan</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>akcook@carolina.rr.com</t>
+          <t>janetnolan6@hotmail.com</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -6935,19 +6939,15 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Riya</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Anto</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>ranto1993@gmail.com</t>
-        </is>
-      </c>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -6957,17 +6957,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>preeti</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Grahn</t>
+          <t>wadhwa</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>robjobgrahn@outlook.com</t>
+          <t>preetiwadhwa87@gmail.com</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -6979,15 +6979,19 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Riya</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Nagpal</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr"/>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>akcook@carolina.rr.com</t>
+        </is>
+      </c>
       <c r="D327" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -6997,17 +7001,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Anto</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>all_temp@hotmail.com</t>
+          <t>ranto1993@gmail.com</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7019,17 +7023,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Vikas</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Sakariya</t>
+          <t>Grahn</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>sakariyavikas@gmail.com</t>
+          <t>robjobgrahn@outlook.com</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -7041,19 +7045,15 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Lyka</t>
+          <t>Riya</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Fresnedi</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>lykafresnedi@gmail.com</t>
-        </is>
-      </c>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -7063,17 +7063,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Graeme</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>McMath</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>gtmcmath@gmail.com</t>
+          <t>all_temp@hotmail.com</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7085,17 +7085,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Vikas</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Seibold</t>
+          <t>Sakariya</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>fatimaseibold@hotmail.com</t>
+          <t>sakariyavikas@gmail.com</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -7107,17 +7107,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Denise</t>
+          <t>Lyka</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Fresnedi</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>denisejanetjones@gmail.com</t>
+          <t>lykafresnedi@gmail.com</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7129,17 +7129,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Neal</t>
+          <t>Graeme</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Bouwneester</t>
+          <t>McMath</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>nbouwmeester@gmail.com</t>
+          <t>gtmcmath@gmail.com</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -7151,17 +7151,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Saurabh</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Chopra</t>
+          <t>Seibold</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>schopra86@live.com</t>
+          <t>fatimaseibold@hotmail.com</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -7173,17 +7173,17 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Kristy</t>
+          <t>Denise</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>MacGregor</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>kristy.hallx@gmail.com</t>
+          <t>denisejanetjones@gmail.com</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -7195,17 +7195,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Chu</t>
+          <t>Neal</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Bouwneester</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>tan.chu1997@gmail.com</t>
+          <t>nbouwmeester@gmail.com</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7217,17 +7217,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Saurabh</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Seibold</t>
+          <t>Chopra</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>dale.seibold@hotmail.com</t>
+          <t>schopra86@live.com</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -7239,20 +7239,1372 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
+          <t>Kristy</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>MacGregor</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>kristy.hallx@gmail.com</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Chu</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Tan</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>tan.chu1997@gmail.com</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Dale</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Seibold</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>dale.seibold@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
           <t>Chris</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B342" t="inlineStr">
         <is>
           <t>Seller</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr">
+      <c r="C342" t="inlineStr">
         <is>
           <t>valandchris@roger.com</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Judges</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>jenniferbattler@gmail.com</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Momina</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Mir</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>biological.engineer@gmail.com</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Tayyab</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Ahmed</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>tayyabahmed561@gmail.com</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Ansharah</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Abdool</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Omar</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Abdool</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>momina.and.omar@gmail.com</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Isla</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Macloud</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>isla20macloud@gmail.com</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Cynthis</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Perri</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>cindyp@charcoalgroup.ca</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Saurabh</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>info@saurabhnagpal.ca</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Mansi</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Chadha</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>mansisegan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Barroso</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>l.barroso@live.ca</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Foulds</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>confirmemail123@gmail.com</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Abe</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Macdonald</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>abesammac@gmail.com</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Jessie</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Tang</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>tjting@gmail.com</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Mandeep</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Evan</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Crossman</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>caley.crossman@gmail.com</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Julian</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Jozsvai</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>julian_007@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Gaurav</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Chadha</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>gauravchadha30@gmail.com</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Maeem</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Mir</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>maeemymir@gmail.com</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Mandeep</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>nagpalmandeep@icloud.com</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Marton</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>joannamarton24@gmail.com</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Burke</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>jennburke2525@gmail.com</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Diane</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Foulds</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>diane.pure@gmail.com</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Nelo</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Tagbacaula</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>nelo75@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Trong</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Hoang</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>trong_227@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Barry</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Saville</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>jbarrysaville@gmail.com</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Val</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Smith-Sellers</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>vsmithsellers@rogers.com</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Ishmam</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Chandan</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>ichandan@septodont.com</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Chanthala</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Luong</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>mluong98@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Huzaifa</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Hatia</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>hatia.huzaifa@icloud.com</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Furqan</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Salam</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>fsalam@live.com</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Sadiq</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Rehman</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>sadiqrehman5@gmail.com</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Moosa</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Sedu</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>moosa.sedu@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Bruno</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Semedo</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>ilovemom_2017@outlook.com</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Jacob</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Sine</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>jacobofsine@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Jayce</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Semedo</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>ilovelmom_2017@outlook.com</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Tracy</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Watters</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>tracy.watters@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Melichercik</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>jmeliche@uoguelph.ca</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Lindsay</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Kennedy</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>lindsay.kennedy2797@gmail.com</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Dennis</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Cabrera</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>denniscabrera231@gmail.com</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Dana</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Sherriff</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>quiettime90@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Braeden</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Snyder</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>braeden.snyder@live.com</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Greg</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Watters</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>gwatters@live.com</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Melichercik</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>markmelichercik@gmail.com</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Paddock</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>ethan.paddock@gmail.com</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Soucie</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>ben.soucie@me.com</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Devansh</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Mehta</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>d33mehta@uwaterloo.ca</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Rohan</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Gambhir</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>rohan.gambhir786@gmail.com</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Anweshika</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Anweshika</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>anweshika.gec@gmail.com</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Hailey</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Atkinson</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>leecatkinson@gmail.com</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Mann</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Mann</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>vishal.mann33@gmail.com</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Saurabh</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>saurabhsingh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Kathryn</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Emms</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>kathrynemms@me.com</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Atienza</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>alexandra.g.atienza@gmail.com</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>oei</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>kyleoei2787@gmail.com</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Manoocehri</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>lapd1356@gmail.com</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Schembri</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>ashley.schembri@gmail.com</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Doug</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Atkinson</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>dougatkinson32@gmail.com</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Linda</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Innanen</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>linda.innanen@gmail.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
         </is>

--- a/docs/downloads/Cambridge.xlsx
+++ b/docs/downloads/Cambridge.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D401"/>
+  <dimension ref="A1:D492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -677,17 +677,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Cesar</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Waring</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>tinalwaring@gmail.com</t>
+          <t>fil-cesar@rogers.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -699,17 +699,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Waring</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fc8833@yahoo.ca</t>
+          <t>tinalwaring@gmail.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -721,17 +721,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Milja</t>
+          <t>Francis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gillespie</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>miljagillespie@gmail.com</t>
+          <t>fc8833@yahoo.ca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -743,17 +743,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Milja</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hannay</t>
+          <t>Gillespie</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>shannay@rogers.com</t>
+          <t>miljagillespie@gmail.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -765,17 +765,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maddie</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Hannay</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>lena28ca@yahoo.com</t>
+          <t>shannay@rogers.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -787,17 +787,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lori</t>
+          <t>Maddie</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Truax</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dltruax@rogers.com</t>
+          <t>lena28ca@yahoo.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -809,17 +809,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Tim</t>
+          <t>Lori</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kesselring</t>
+          <t>Truax</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>timkesselring33@gmail.com</t>
+          <t>dltruax@rogers.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -831,17 +831,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mary</t>
+          <t>Tim</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hayes</t>
+          <t>Kesselring</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>phrednlare@hotmail.com</t>
+          <t>timkesselring33@gmail.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -853,17 +853,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alan</t>
+          <t>Mary</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Couch</t>
+          <t>Hayes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ajcouch2021@gmail.com</t>
+          <t>phrednlare@hotmail.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -875,17 +875,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Katie</t>
+          <t>Alan</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kesselring</t>
+          <t>Couch</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>katiekesselring@gmail.com</t>
+          <t>ajcouch2021@gmail.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -897,17 +897,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kamil</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Machnik</t>
+          <t>Bout</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kamil.machnik@hotmail.com</t>
+          <t>barbarabout@gmail.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -919,17 +919,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rev</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jayakumar</t>
+          <t>Kesselring</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>revjk18@gmail.com</t>
+          <t>katiekesselring@gmail.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -941,17 +941,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Kamil</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Mercier</t>
+          <t>Machnik</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dalemercier6193@gmail.com</t>
+          <t>kamil.machnik@hotmail.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -963,17 +963,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Blair</t>
+          <t>Rebecca</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mcdonald</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>blairmcdonald.ca@gmail.com</t>
+          <t>bwg081318@gmail.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bojan</t>
+          <t>Rev</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Batricevic</t>
+          <t>Jayakumar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>bojanbatricevic@gmail.com</t>
+          <t>revjk18@gmail.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1007,17 +1007,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Asif</t>
+          <t>Dale</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alidina</t>
+          <t>Mercier</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>asif+@pickleplexclub.ca</t>
+          <t>dalemercier6193@gmail.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1029,17 +1029,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Blair</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Bailey</t>
+          <t>Mcdonald</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ksbailey@yahoo.com</t>
+          <t>blairmcdonald.ca@gmail.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Bojan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bridgman</t>
+          <t>Batricevic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>susan_bridge@live.ca</t>
+          <t>bojanbatricevic@gmail.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Siya</t>
+          <t>Asif</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sood</t>
+          <t>Alidina</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>siyasood1107@gmail.com</t>
+          <t>asif+@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1095,17 +1095,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Polzin</t>
+          <t>Bailey</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>polzinlandscaping@me.com</t>
+          <t>ksbailey@yahoo.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1117,17 +1117,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Bryce</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rawn</t>
+          <t>Bridgman</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>brycerawn18@gmail.com</t>
+          <t>susan_bridge@live.ca</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1139,17 +1139,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Siya</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Csaszar</t>
+          <t>Sood</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>matthewcsaszar@gmail.com</t>
+          <t>siyasood1107@gmail.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1161,17 +1161,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Pat</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Grasso</t>
+          <t>Polzin</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>pat.grasso@togers.com</t>
+          <t>polzinlandscaping@me.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1183,17 +1183,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nghia</t>
+          <t>Bryce</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Duong</t>
+          <t>Rawn</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>nghiadduong@gmail.com</t>
+          <t>brycerawn18@gmail.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sponder</t>
+          <t>Csaszar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>chris.sponder@gmail.com</t>
+          <t>matthewcsaszar@gmail.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1227,17 +1227,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Pat</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pickleplex</t>
+          <t>Grasso</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cambridge@pickleplexclub.ca</t>
+          <t>pat.grasso@togers.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1249,17 +1249,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Nghia</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bradshaw</t>
+          <t>Duong</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>abradshaw435@gmail.com</t>
+          <t>nghiadduong@gmail.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Vince</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Colanardi</t>
+          <t>Sponder</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>vincevince2929@hotmail.com</t>
+          <t>chris.sponder@gmail.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1293,17 +1293,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Maureen</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Juniper</t>
+          <t>Pickleplex</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>maureen@praxispr.ca</t>
+          <t>cambridge@pickleplexclub.ca</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alviano</t>
+          <t>Bradshaw</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>lisaa@rogers.com</t>
+          <t>abradshaw435@gmail.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dean</t>
+          <t>Vince</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Colanardi</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>deanjmac@yahoo.ca</t>
+          <t>vincevince2929@hotmail.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Maureen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Francis</t>
+          <t>Juniper</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jay@pickleplexclub.ca</t>
+          <t>maureen@praxispr.ca</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,17 +1381,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Yong</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Liu</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>yon_liu@hotmail.com</t>
+          <t>ecoelho212@gmail.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1403,17 +1403,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Leiskau</t>
+          <t>Alviano</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>kara@jdgraphics.com</t>
+          <t>lisaa@rogers.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1425,15 +1425,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Devanshi</t>
+          <t>Dean</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mistry</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>Macdonald</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>deanjmac@yahoo.ca</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1443,15 +1447,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Beckett</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>Francis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>jay@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1461,15 +1469,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dallas</t>
+          <t>Yong</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Brown</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>Liu</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>yon_liu@hotmail.com</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1479,15 +1491,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Amaya</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ismail</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Leiskau</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>kara@jdgraphics.com</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1497,12 +1513,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Paige</t>
+          <t>Devanshi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pilkey</t>
+          <t>Mistry</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1515,7 +1531,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Finnley</t>
+          <t>Beckett</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1533,12 +1549,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Dallas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pilkey</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1551,12 +1567,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marigold</t>
+          <t>Amaya</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Ismail</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1569,12 +1585,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Madison</t>
+          <t>Paige</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Kollar</t>
+          <t>Pilkey</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1587,12 +1603,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kavir</t>
+          <t>Finnley</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1605,7 +1621,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1623,12 +1639,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Anise</t>
+          <t>Marigold</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ismail</t>
+          <t>Brown</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1641,12 +1657,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Silas</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pharoah</t>
+          <t>Kollar</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1659,19 +1675,15 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Hilda</t>
+          <t>Kavir</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dusek</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>mhdudek@gmail.com</t>
-        </is>
-      </c>
+          <t>Patel</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1681,12 +1693,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Verne</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pharoah</t>
+          <t>Pilkey</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1699,12 +1711,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Anise</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Souza Cefrin da Silva</t>
+          <t>Ismail</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1717,12 +1729,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Wesley</t>
+          <t>Silas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Yuricek</t>
+          <t>Pharoah</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1735,15 +1747,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sayali</t>
+          <t>Hilda</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Parkhi</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Dusek</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>mhdudek@gmail.com</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -1753,12 +1769,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Gabby</t>
+          <t>Verne</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Pharoah</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1771,12 +1787,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>Souza Cefrin da Silva</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1789,12 +1805,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Rhonda</t>
+          <t>Wesley</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kalverda</t>
+          <t>Yuricek</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1807,12 +1823,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Reagan</t>
+          <t>Sayali</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>Parkhi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1825,12 +1841,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Gabby</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Martins</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1843,12 +1859,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Yuricek</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1861,12 +1877,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Devan</t>
+          <t>Rhonda</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bhatt</t>
+          <t>Kalverda</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1879,12 +1895,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>brian</t>
+          <t>Reagan</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>le</t>
+          <t>West</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1897,12 +1913,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stead</t>
+          <t>Martins</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1915,12 +1931,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Brady</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Hicks</t>
+          <t>Yuricek</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1933,12 +1949,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Armen</t>
+          <t>Devan</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kabakian</t>
+          <t>Bhatt</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1951,12 +1967,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kaiya</t>
+          <t>brian</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>le</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1969,12 +1985,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Greyson</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>Stead</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1987,12 +2003,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Brady</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>Hicks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -2005,12 +2021,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Armen</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ottman</t>
+          <t>Kabakian</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -2023,12 +2039,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Grayson</t>
+          <t>Kaiya</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Taneza</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -2041,12 +2057,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Greyson</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -2059,12 +2075,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Theo</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Baxter</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -2077,12 +2093,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Valeria</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mencia</t>
+          <t>Ottman</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -2095,19 +2111,15 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Grayson</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>De almeida</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>daniel.abeldealmeida@gmail.com</t>
-        </is>
-      </c>
+          <t>Taneza</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2117,12 +2129,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cesar</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jauregui</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -2135,12 +2147,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Theo</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dandrea</t>
+          <t>Baxter</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2153,12 +2165,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Valeria</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Diaz</t>
+          <t>Mencia</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2171,15 +2183,19 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ripley</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Matheson</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
+          <t>De almeida</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>daniel.abeldealmeida@gmail.com</t>
+        </is>
+      </c>
       <c r="D87" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2189,19 +2205,15 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Jean-paul</t>
+          <t>Cesar</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Morgan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>morganjea18@gmail.com</t>
-        </is>
-      </c>
+          <t>Jauregui</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2211,12 +2223,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>POOJA</t>
+          <t>Carlos</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pawar</t>
+          <t>Dandrea</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2229,12 +2241,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Neel</t>
+          <t>Isabella</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Gondalia</t>
+          <t>Diaz</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2247,12 +2259,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Ripley</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sharp</t>
+          <t>Matheson</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2265,15 +2277,19 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Jean-paul</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sharma</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
+          <t>Morgan</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>morganjea18@gmail.com</t>
+        </is>
+      </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2283,12 +2299,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>POOJA</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Duong</t>
+          <t>Pawar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2301,12 +2317,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Neel</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Gondalia</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2319,12 +2335,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Clara</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Sharp</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2337,12 +2353,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Maxwell</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Mondor</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2355,12 +2371,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>McDonald</t>
+          <t>Duong</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2373,19 +2389,15 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Richmond</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>5116rpb@gmail.com</t>
-        </is>
-      </c>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2395,12 +2407,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Clara</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Beck</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2413,7 +2425,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nora</t>
+          <t>Maxwell</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2431,12 +2443,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Payton</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Marr</t>
+          <t>McDonald</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2449,15 +2461,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Raphael</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>5116rpb@gmail.com</t>
+        </is>
+      </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2467,19 +2483,15 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Player</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>rplayer.4050@gmail.com</t>
-        </is>
-      </c>
+          <t>Beck</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2489,12 +2501,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Nora</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Coelho</t>
+          <t>Mondor</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2507,19 +2519,15 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Will</t>
+          <t>Payton</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Law</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>solis.environmental@gmail.com</t>
-        </is>
-      </c>
+          <t>Marr</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2529,12 +2537,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Raphael</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Coelho</t>
+          <t>Del Rosario</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2547,7 +2555,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2555,7 +2563,11 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>rplayer.4050@gmail.com</t>
+        </is>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2565,7 +2577,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2583,15 +2595,19 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Will</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nguyen</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>Law</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>solis.environmental@gmail.com</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2601,12 +2617,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>King</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2619,12 +2635,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Jim</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ballard</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2637,12 +2653,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Prachi</t>
+          <t>Amelia</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>Coelho</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2655,12 +2671,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Rolleman</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2673,7 +2689,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2691,12 +2707,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Katrina</t>
+          <t>Jim</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kools</t>
+          <t>Ballard</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2709,12 +2725,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Elissa</t>
+          <t>Prachi</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Patel</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2727,12 +2743,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Suzy</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Rolleman</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2745,12 +2761,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Huo</t>
+          <t>King</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2763,12 +2779,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Katrina</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Kools</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2781,12 +2797,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Elissa</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Snook</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2799,12 +2815,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Jobathan</t>
+          <t>Suzy</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Huo</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2817,12 +2833,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Huo</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2835,12 +2851,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Jun</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Huo</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2853,12 +2869,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Snook</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2871,12 +2887,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Cody</t>
+          <t>Jobathan</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Fry</t>
+          <t>Huo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2889,12 +2905,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Paula</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lannutti</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2907,19 +2923,15 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Jasper</t>
+          <t>Jun</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Viado</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>jasper@pickleplexclub.ca</t>
-        </is>
-      </c>
+          <t>Huo</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2929,12 +2941,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Davis</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Huehn</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2947,19 +2959,15 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Dhuha</t>
+          <t>Cody</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Chaudhry</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>dhuha123@live.ca</t>
-        </is>
-      </c>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -2969,12 +2977,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Declan</t>
+          <t>Paula</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Huehn</t>
+          <t>Lannutti</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2987,15 +2995,19 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Lacey</t>
+          <t>Jasper</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Huehn</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
+          <t>Viado</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>jasper@pickleplexclub.ca</t>
+        </is>
+      </c>
       <c r="D131" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3005,12 +3017,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Davis</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ritchie</t>
+          <t>Huehn</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3023,15 +3035,19 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Dhuha</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Ritchie</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>Chaudhry</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>dhuha123@live.ca</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3041,19 +3057,15 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Morgan</t>
+          <t>Declan</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Mcallister</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>josh027girl@gmail.com</t>
-        </is>
-      </c>
+          <t>Huehn</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3063,12 +3075,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Lacey</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Hardy</t>
+          <t>Huehn</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3081,12 +3093,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>An</t>
+          <t>Ritchie</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3099,12 +3111,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Thomas</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Ritchie</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3117,15 +3129,19 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Eliot</t>
+          <t>Morgan</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr"/>
+          <t>Mcallister</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>josh027girl@gmail.com</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3135,7 +3151,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Elliott</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3153,12 +3169,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Kerr</t>
+          <t>An</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3171,19 +3187,15 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Joe</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Amaral</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>jameralc522@rogers.com</t>
-        </is>
-      </c>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3193,19 +3205,15 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Zohra</t>
+          <t>Eliot</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Kharodia</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>zohra_kharodia@hotmail.com</t>
-        </is>
-      </c>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3215,12 +3223,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Elliott</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Kerr</t>
+          <t>Hardy</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3233,19 +3241,15 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Jay</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Sandhu</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>jay@registon.ca</t>
-        </is>
-      </c>
+          <t>Kerr</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3255,17 +3259,17 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sheila</t>
+          <t>Joe</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Anonuevo</t>
+          <t>Amaral</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>sheila.anonuevo@gmail.com</t>
+          <t>jameralc522@rogers.com</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -3277,17 +3281,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Zohra</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Guest</t>
+          <t>Kharodia</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>guest123$@hotmail.com</t>
+          <t>zohra_kharodia@hotmail.com</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -3299,19 +3303,15 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Mufaddal</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Jerwalla</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>mufaddaljerwalla@gmail.com</t>
-        </is>
-      </c>
+          <t>Kerr</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3321,15 +3321,19 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Jay</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Stewart</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr"/>
+          <t>Sandhu</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>jay@registon.ca</t>
+        </is>
+      </c>
       <c r="D148" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3339,15 +3343,19 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Grady</t>
+          <t>Sheila</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>More</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr"/>
+          <t>Anonuevo</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>sheila.anonuevo@gmail.com</t>
+        </is>
+      </c>
       <c r="D149" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3357,17 +3365,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Caroleann</t>
+          <t>Guest</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Fleming</t>
+          <t>Guest</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>carbyckshank@bell.net</t>
+          <t>guest123$@hotmail.com</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3379,15 +3387,19 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Gwen</t>
+          <t>Mufaddal</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dias</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
+          <t>Jerwalla</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>mufaddaljerwalla@gmail.com</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3397,12 +3409,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Jaxon</t>
+          <t>Kyle</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Vacon</t>
+          <t>Stewart</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3415,19 +3427,15 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Grady</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Phan</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>phanmyster@gmail.com</t>
-        </is>
-      </c>
+          <t>More</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3437,17 +3445,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Elie</t>
+          <t>Caroleann</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Daccache</t>
+          <t>Fleming</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>d.elie@ymail.com</t>
+          <t>carbyckshank@bell.net</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3459,12 +3467,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Gwen</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Ferguson</t>
+          <t>Dias</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3477,12 +3485,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Jaxon</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Reiber</t>
+          <t>Vacon</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3495,15 +3503,19 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sayavong</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr"/>
+          <t>Phan</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>phanmyster@gmail.com</t>
+        </is>
+      </c>
       <c r="D157" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3513,17 +3525,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>Elie</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Thirtle</t>
+          <t>Daccache</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>sthirtle@rogers.com</t>
+          <t>d.elie@ymail.com</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3535,12 +3547,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Samantha</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Lockner</t>
+          <t>Ferguson</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3553,12 +3565,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Milo</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Moodley</t>
+          <t>Reiber</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3571,19 +3583,15 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Walls</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>abbydeane05@icloud.com</t>
-        </is>
-      </c>
+          <t>Sayavong</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3593,17 +3601,17 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Walls</t>
+          <t>Thirtle</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>shanny.deane@gmail.com</t>
+          <t>sthirtle@rogers.com</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -3615,19 +3623,15 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Nafisa</t>
+          <t>Samantha</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Unia</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>nafisaunia1971@gmail.com</t>
-        </is>
-      </c>
+          <t>Lockner</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
       <c r="D163" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3637,19 +3641,15 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Milo</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Elsden</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>maxelsden@gmail.com</t>
-        </is>
-      </c>
+          <t>Moodley</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3659,17 +3659,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Cymbalski</t>
+          <t>Walls</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>john.cymbalski@gmail.com</t>
+          <t>abbydeane05@icloud.com</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -3681,17 +3681,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Tony</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Dawe</t>
+          <t>Walls</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>rtdawe@icloud.com</t>
+          <t>shanny.deane@gmail.com</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -3703,17 +3703,17 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Arul</t>
+          <t>Nafisa</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Kumar</t>
+          <t>Unia</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>dinsboyjr@gmail.com</t>
+          <t>nafisaunia1971@gmail.com</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -3725,17 +3725,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Vedansh</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Kokra</t>
+          <t>Elsden</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>vedansh.kokra@icloud.com</t>
+          <t>maxelsden@gmail.com</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -3747,17 +3747,17 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>elisabeth</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>eden</t>
+          <t>Cymbalski</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>elisabeth.eden12@gmail.com</t>
+          <t>john.cymbalski@gmail.com</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -3769,17 +3769,17 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ron</t>
+          <t>Tony</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Genovese</t>
+          <t>Dawe</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>genoveseron9@gmail.com</t>
+          <t>rtdawe@icloud.com</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -3791,17 +3791,17 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Zachary</t>
+          <t>Arul</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Janzen</t>
+          <t>Kumar</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>zacharyj115@gmail.com</t>
+          <t>dinsboyjr@gmail.com</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -3813,17 +3813,17 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Mabel</t>
+          <t>Vedansh</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Dawe</t>
+          <t>Kokra</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>mabeldawe@msn.com</t>
+          <t>vedansh.kokra@icloud.com</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -3835,17 +3835,17 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Advait</t>
+          <t>elisabeth</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Shah</t>
+          <t>eden</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>advaitshah323@gmail.com</t>
+          <t>elisabeth.eden12@gmail.com</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -3857,17 +3857,17 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Connie</t>
+          <t>Ron</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Parsons</t>
+          <t>Genovese</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>david.parsons4@sympatico.ca</t>
+          <t>genoveseron9@gmail.com</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -3879,17 +3879,17 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Zachary</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Yang - t</t>
+          <t>Janzen</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>yang.julie519@trial.ca</t>
+          <t>zacharyj115@gmail.com</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -3901,17 +3901,17 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Mabel</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Maier</t>
+          <t>Dawe</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>shannonmaier@gmail.com</t>
+          <t>mabeldawe@msn.com</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -3923,17 +3923,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Advait</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Awakian</t>
+          <t>Shah</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>jack@tricityflooring.ca</t>
+          <t>advaitshah323@gmail.com</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -3945,15 +3945,19 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Macy</t>
+          <t>Connie</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr"/>
+          <t>Parsons</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>david.parsons4@sympatico.ca</t>
+        </is>
+      </c>
       <c r="D178" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3963,15 +3967,19 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ainsworth</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr"/>
+          <t>Yang - t</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>yang.julie519@trial.ca</t>
+        </is>
+      </c>
       <c r="D179" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3981,15 +3989,19 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Ainsley</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr"/>
+          <t>Maier</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>shannonmaier@gmail.com</t>
+        </is>
+      </c>
       <c r="D180" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -3999,15 +4011,19 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Inaya</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Sajid</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr"/>
+          <t>Awakian</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>jack@tricityflooring.ca</t>
+        </is>
+      </c>
       <c r="D181" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4017,12 +4033,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Zayan</t>
+          <t>Macy</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Sajid</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4035,12 +4051,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Giselle</t>
+          <t>Ainsworth</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Del Rosario</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C183" t="inlineStr"/>
@@ -4053,12 +4069,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Ainsley</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Waring</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="C184" t="inlineStr"/>
@@ -4071,12 +4087,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Inaya</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Sajid</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -4089,12 +4105,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Rian</t>
+          <t>Zayan</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Sajid</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4107,12 +4123,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Tesia</t>
+          <t>Giselle</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Del Rosario</t>
         </is>
       </c>
       <c r="C187" t="inlineStr"/>
@@ -4125,19 +4141,15 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Elisabeth</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bajet</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>eilbajet@gmail.com</t>
-        </is>
-      </c>
+          <t>Waring</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4147,19 +4159,15 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Tailem</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Gingras</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>tag2005@icloud.com</t>
-        </is>
-      </c>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4169,19 +4177,15 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>jill</t>
+          <t>Rian</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>singleton</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>guest.guest@gmail.com</t>
-        </is>
-      </c>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4191,19 +4195,15 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Shannon</t>
+          <t>Tesia</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Blacker</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>blacker.shannon@gmail.com</t>
-        </is>
-      </c>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4213,17 +4213,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Elisabeth</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Furtado</t>
+          <t>Bajet</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>sydneyfurtado06@gmail.com</t>
+          <t>eilbajet@gmail.com</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4235,17 +4235,17 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Tailem</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Bauer</t>
+          <t>Gingras</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>hikeradk04@yahoo.com</t>
+          <t>tag2005@icloud.com</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -4257,17 +4257,17 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>jill</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Perryman</t>
+          <t>singleton</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>sandyperryman59#1@gmail.com</t>
+          <t>guest.guest@gmail.com</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -4279,17 +4279,17 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Shannon</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Beaudoin</t>
+          <t>Blacker</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>laurenbeaudoin@hotmail.com</t>
+          <t>blacker.shannon@gmail.com</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4301,15 +4301,19 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Krishaa</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Makkar</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr"/>
+          <t>Furtado</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>sydneyfurtado06@gmail.com</t>
+        </is>
+      </c>
       <c r="D196" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4319,15 +4323,19 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Kunsh</t>
+          <t>Douglas</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Makkar</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr"/>
+          <t>Bauer</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>hikeradk04@yahoo.com</t>
+        </is>
+      </c>
       <c r="D197" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4337,17 +4345,17 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Senecal</t>
+          <t>Perryman</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>letournicoteur@gmail.com</t>
+          <t>sandyperryman59#1@gmail.com</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -4359,15 +4367,19 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Giusmukh</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr"/>
+          <t>Beaudoin</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>laurenbeaudoin@hotmail.com</t>
+        </is>
+      </c>
       <c r="D199" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4377,12 +4389,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Amandeep</t>
+          <t>Krishaa</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Makkar</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4395,12 +4407,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Teghveer</t>
+          <t>Kunsh</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Makkar</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4413,15 +4425,19 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Kaemanveer</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Singh</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr"/>
+          <t>Senecal</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>letournicoteur@gmail.com</t>
+        </is>
+      </c>
       <c r="D202" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4431,12 +4447,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Tina</t>
+          <t>Giusmukh</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Waring</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4449,12 +4465,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Idrees</t>
+          <t>Amandeep</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Bijabhai</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4467,12 +4483,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ziyaad</t>
+          <t>Teghveer</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Bijabhai</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4485,19 +4501,15 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Kaemanveer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Pley</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>mpley9800@gmail.com</t>
-        </is>
-      </c>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4507,19 +4519,15 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Jose</t>
+          <t>Tina</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Ameral</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>email1233@email.com</t>
-        </is>
-      </c>
+          <t>Waring</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4529,19 +4537,15 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Helen</t>
+          <t>Idrees</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Contreras</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>helen@cartwheelcare.org</t>
-        </is>
-      </c>
+          <t>Bijabhai</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4551,19 +4555,15 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Kyungjin</t>
+          <t>Ziyaad</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Peters</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>aw_peters@yahoo.com</t>
-        </is>
-      </c>
+          <t>Bijabhai</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4573,17 +4573,17 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Matt</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Havell</t>
+          <t>Pley</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>njhavell@gmail.com</t>
+          <t>mpley9800@gmail.com</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -4595,17 +4595,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Jose</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Agiannidis</t>
+          <t>Ameral</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>mikee_911@hotmail.com</t>
+          <t>email1233@email.com</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -4617,15 +4617,19 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Leeja</t>
+          <t>Helen</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Hajak</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
+          <t>Contreras</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>helen@cartwheelcare.org</t>
+        </is>
+      </c>
       <c r="D212" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4635,15 +4639,19 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Niyah</t>
+          <t>Kyungjin</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Hajak</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr"/>
+          <t>Peters</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>aw_peters@yahoo.com</t>
+        </is>
+      </c>
       <c r="D213" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4653,15 +4661,19 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Matt</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>McCracken</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
+          <t>Havell</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>njhavell@gmail.com</t>
+        </is>
+      </c>
       <c r="D214" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4671,15 +4683,19 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Susan</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Gloria</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr"/>
+          <t>Agiannidis</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>mikee_911@hotmail.com</t>
+        </is>
+      </c>
       <c r="D215" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4689,17 +4705,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Philip</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Bistretzan</t>
+          <t>Rivera HONCHO</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>philip.bistretzan@gmail.com</t>
+          <t>ana.rivera@honchopickle.com</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -4711,19 +4727,15 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Leeja</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Alexander</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>jaysalexander78@gmail.com</t>
-        </is>
-      </c>
+          <t>Hajak</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4733,12 +4745,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Gavin</t>
+          <t>Niyah</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Moogk</t>
+          <t>Hajak</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4751,19 +4763,15 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Laurie</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Morrison</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>lmorrison@swuftpearlprocess.ca</t>
-        </is>
-      </c>
+          <t>McCracken</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4773,19 +4781,15 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Macel</t>
+          <t>Susan</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Richard</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>marcelrichardrealtor@gmauil.com</t>
-        </is>
-      </c>
+          <t>Gloria</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4795,15 +4799,19 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Philip</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Moogk</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr"/>
+          <t>Bistretzan</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>philip.bistretzan@gmail.com</t>
+        </is>
+      </c>
       <c r="D221" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4813,15 +4821,19 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Leonardo</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr"/>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>jaysalexander78@gmail.com</t>
+        </is>
+      </c>
       <c r="D222" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4831,12 +4843,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>AJ</t>
+          <t>Gavin</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Moogk</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -4849,15 +4861,19 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Laurie</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Leonardo</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr"/>
+          <t>Morrison</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>lmorrison@swuftpearlprocess.ca</t>
+        </is>
+      </c>
       <c r="D224" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4867,15 +4883,19 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Peyton</t>
+          <t>Macel</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Leonardo</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr"/>
+          <t>Richard</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>marcelrichardrealtor@gmauil.com</t>
+        </is>
+      </c>
       <c r="D225" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -4885,12 +4905,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Sami</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Siddiqi</t>
+          <t>Moogk</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4903,12 +4923,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Finnley</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Tams</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4921,12 +4941,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>AJ</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Parteno</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4939,12 +4959,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>parteno</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4957,12 +4977,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Saifaan</t>
+          <t>Peyton</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Siddiqi</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4975,12 +4995,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Winter</t>
+          <t>Sami</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Tams</t>
+          <t>Siddiqi</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -4993,12 +5013,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Alya</t>
+          <t>Finnley</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Tams</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -5011,12 +5031,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Salman</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Parteno</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -5029,12 +5049,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Amal</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Ahmad</t>
+          <t>parteno</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -5047,12 +5067,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Rumi</t>
+          <t>Saifaan</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Rehan</t>
+          <t>Siddiqi</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -5065,12 +5085,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Azlan</t>
+          <t>Winter</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Ahmad</t>
+          <t>Tams</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -5083,19 +5103,15 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Hashim</t>
+          <t>Alya</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Vekar</t>
-        </is>
-      </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>hashim.vekar@gmail.com</t>
-        </is>
-      </c>
+          <t>Khan</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5105,12 +5121,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Nora</t>
+          <t>Salman</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Mondor</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5123,12 +5139,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Camden</t>
+          <t>Amal</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Ahmad</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -5141,12 +5157,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>MacKenzie</t>
+          <t>Rumi</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Lennon</t>
+          <t>Rehan</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5159,12 +5175,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Azlan</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Ahmad</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5177,15 +5193,19 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>calla</t>
+          <t>Hashim</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Tams</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
+          <t>Vekar</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>hashim.vekar@gmail.com</t>
+        </is>
+      </c>
       <c r="D242" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5195,19 +5215,15 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>james</t>
+          <t>Nora</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>burger</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>jamesburger@gmail.com</t>
-        </is>
-      </c>
+          <t>Mondor</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5217,12 +5233,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Pierce</t>
+          <t>Camden</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Trott</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5235,12 +5251,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Josephine</t>
+          <t>MacKenzie</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Doan</t>
+          <t>Lennon</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5253,19 +5269,15 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>WAYNE</t>
+          <t>Mason</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PANSEGRAU</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>wayne@topshelfarena.com</t>
-        </is>
-      </c>
+          <t>Koch</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5275,12 +5287,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Darren</t>
+          <t>calla</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Galway</t>
+          <t>Tams</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5293,15 +5305,19 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>james</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Ropp</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr"/>
+          <t>burger</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>jamesburger@gmail.com</t>
+        </is>
+      </c>
       <c r="D248" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5311,12 +5327,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Benson</t>
+          <t>Pierce</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Ropp</t>
+          <t>Trott</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -5329,12 +5345,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Jade</t>
+          <t>Josephine</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Rosebruch</t>
+          <t>Doan</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5347,15 +5363,19 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Paisley</t>
+          <t>WAYNE</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Lobbezoo</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr"/>
+          <t>PANSEGRAU</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>wayne@topshelfarena.com</t>
+        </is>
+      </c>
       <c r="D251" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5365,19 +5385,15 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Summerr</t>
+          <t>Darren</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Baadani</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>summerbaad@gmail.com</t>
-        </is>
-      </c>
+          <t>Galway</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5387,12 +5403,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Juilen</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Hobani</t>
+          <t>Ropp</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5405,12 +5421,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Jori</t>
+          <t>Benson</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Hobani</t>
+          <t>Ropp</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5423,19 +5439,15 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Jade</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Ives</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>saranives@gmail.com</t>
-        </is>
-      </c>
+          <t>Rosebruch</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5445,19 +5457,15 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Paisley</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Bigras</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>drewbigras@outlook.com</t>
-        </is>
-      </c>
+          <t>Lobbezoo</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5467,15 +5475,19 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Abeer</t>
+          <t>Summerr</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Adaini</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr"/>
+          <t>Baadani</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>summerbaad@gmail.com</t>
+        </is>
+      </c>
       <c r="D257" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5485,12 +5497,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Daniyah</t>
+          <t>Juilen</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Ahmad</t>
+          <t>Hobani</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5503,12 +5515,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Anwar</t>
+          <t>Jori</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Ahmad</t>
+          <t>Hobani</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5521,17 +5533,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Eyob</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Gebregziabher</t>
+          <t>Ives</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>boyeyob@gmail.com</t>
+          <t>saranives@gmail.com</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -5543,17 +5555,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Rajdeep</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Samra</t>
+          <t>Bigras</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>samrar1945@gmail.com</t>
+          <t>drewbigras@outlook.com</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -5565,19 +5577,15 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Rassel</t>
+          <t>Abeer</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Padillo</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>padillorassel@rocketmail.com</t>
-        </is>
-      </c>
+          <t>Adaini</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5587,19 +5595,15 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Ramzi</t>
+          <t>Daniyah</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Hobani</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>hobaniramzi@gmail.com</t>
-        </is>
-      </c>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5609,19 +5613,15 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Renna</t>
+          <t>Anwar</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Baadani</t>
-        </is>
-      </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>rennab883@yahoo.com</t>
-        </is>
-      </c>
+          <t>Ahmad</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5631,17 +5631,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Yousef</t>
+          <t>Eyob</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>ahmad</t>
+          <t>Gebregziabher</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>yousef.dayani22@gmail.com</t>
+          <t>boyeyob@gmail.com</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -5653,15 +5653,19 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Layan</t>
+          <t>Rajdeep</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Ahmad</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr"/>
+          <t>Samra</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>samrar1945@gmail.com</t>
+        </is>
+      </c>
       <c r="D266" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5671,17 +5675,17 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Tayden</t>
+          <t>Rassel</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Figueiredo</t>
+          <t>Padillo</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>tayden.fig@gmail.com</t>
+          <t>padillorassel@rocketmail.com</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -5693,17 +5697,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Ramzi</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Bushnell</t>
+          <t>Hobani</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>bushnelljacob24@gmail.com</t>
+          <t>hobaniramzi@gmail.com</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -5715,17 +5719,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Renna</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Inacio</t>
+          <t>Baadani</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>xavierinacio27@gmail.com</t>
+          <t>rennab883@yahoo.com</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -5737,17 +5741,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Linda</t>
+          <t>Yousef</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Morsink</t>
+          <t>ahmad</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>lmorsink4@gmail.com</t>
+          <t>yousef.dayani22@gmail.com</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -5759,12 +5763,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Layan</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Ahmad</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -5777,15 +5781,19 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Brandon Scott</t>
+          <t>Tayden</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Chow</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr"/>
+          <t>Figueiredo</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>tayden.fig@gmail.com</t>
+        </is>
+      </c>
       <c r="D272" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5795,17 +5803,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Nadine</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Sison</t>
+          <t>Bushnell</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>sisonmaranadine@gmail.com</t>
+          <t>bushnelljacob24@gmail.com</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -5817,17 +5825,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Angie</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Inacio</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>markangpost@gmail.com</t>
+          <t>xavierinacio27@gmail.com</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -5839,17 +5847,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Linda</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Goodfellow</t>
+          <t>Morsink</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>jason.chorney@gmail.com</t>
+          <t>lmorsink4@gmail.com</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -5861,19 +5869,15 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Dean</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>ethandean427@gmail.com</t>
-        </is>
-      </c>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5883,19 +5887,15 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Brandon Scott</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Nguyen</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>eatmeh2007@yahoo.com</t>
-        </is>
-      </c>
+          <t>Chow</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -5905,17 +5905,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Angie</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>haileynguyen2012@gmail.com</t>
+          <t>markangpost@gmail.com</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -5927,17 +5927,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Sophie</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Goodfellow</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>sophienguyen1507@gmail.com</t>
+          <t>jason.chorney@gmail.com</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -5949,17 +5949,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Jasleen</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Hans</t>
+          <t>Dean</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>jhans20016@gmail.com</t>
+          <t>ethandean427@gmail.com</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -5971,17 +5971,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Coghill</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>jcoghill1@outlook.com</t>
+          <t>eatmeh2007@yahoo.com</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -5993,17 +5993,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>curtisbabg99@gmail.com</t>
+          <t>haileynguyen2012@gmail.com</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -6015,17 +6015,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>dave</t>
+          <t>Sophie</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>serpa</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>simplymasonry@gmail.com</t>
+          <t>sophienguyen1507@gmail.com</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -6037,17 +6037,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Neal</t>
+          <t>Jasleen</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Bouwneester</t>
+          <t>Hans</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>neal.bouwmeester@gmail.com</t>
+          <t>jhans20016@gmail.com</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -6059,17 +6059,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Tyson</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Coghill</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>tysongood103@gmail.com</t>
+          <t>jcoghill1@outlook.com</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -6081,7 +6081,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Grace</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>graceebaby99@gmail.com</t>
+          <t>curtisbabg99@gmail.com</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -6103,17 +6103,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Cameryn</t>
+          <t>dave</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Rocha</t>
+          <t>serpa</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>camerynrochaa4@gmail.com</t>
+          <t>simplymasonry@gmail.com</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -6125,17 +6125,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Neal</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>De Sousa</t>
+          <t>Bouwneester</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>dannydsoccer@gmail.com</t>
+          <t>neal.bouwmeester@gmail.com</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -6147,17 +6147,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>Tyson</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Perri</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>vinnyp19@icloud.com</t>
+          <t>tysongood103@gmail.com</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6169,17 +6169,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Grace</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Goldberg-Rogers</t>
+          <t>Baby</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ryangoldbergrogers@gmail.com</t>
+          <t>graceebaby99@gmail.com</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6191,17 +6191,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Cameryn</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Baby</t>
+          <t>Rocha</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>curtisbaby99@gmail.com</t>
+          <t>camerynrochaa4@gmail.com</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -6213,17 +6213,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Seda</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Ertabak</t>
+          <t>De Sousa</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>sedaertabak@hotmail.com</t>
+          <t>dannydsoccer@gmail.com</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -6235,17 +6235,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Ali</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Ossman</t>
+          <t>Perri</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>aliossman1234@outlook.com</t>
+          <t>vinnyp19@icloud.com</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -6257,17 +6257,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>duong</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>nguyen</t>
+          <t>Goldberg-Rogers</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>d.spam0707@gmail.com</t>
+          <t>ryangoldbergrogers@gmail.com</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -6279,17 +6279,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Khan</t>
+          <t>Baby</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>fatimak372@gmail.com</t>
+          <t>curtisbaby99@gmail.com</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -6301,17 +6301,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Jibraan</t>
+          <t>Jeanette</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Salam</t>
+          <t>Carnegie</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>jibraan.salam@gmail.com</t>
+          <t>jcarnegie5@hotmail.com</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -6323,7 +6323,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Kevin (Kerem)</t>
+          <t>Seda</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>kevinertabak@gmail.com</t>
+          <t>sedaertabak@hotmail.com</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6345,17 +6345,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Ria</t>
+          <t>Ali</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Oanes</t>
+          <t>Ossman</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>oaneslaw@gmail.com</t>
+          <t>aliossman1234@outlook.com</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6367,17 +6367,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>duong</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Caskie</t>
+          <t>nguyen</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>jencaskie@gmail.com</t>
+          <t>d.spam0707@gmail.com</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -6389,17 +6389,17 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Dekort</t>
+          <t>Khan</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>jordandekort@gmail.com</t>
+          <t>fatimak372@gmail.com</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -6411,17 +6411,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Don</t>
+          <t>Jibraan</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Oanes</t>
+          <t>Salam</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>kamonte311@yahoo.com</t>
+          <t>jibraan.salam@gmail.com</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -6433,17 +6433,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Abby</t>
+          <t>Kevin (Kerem)</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Green</t>
+          <t>Ertabak</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>abby06green@gmail.com</t>
+          <t>kevinertabak@gmail.com</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -6455,17 +6455,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Caleb</t>
+          <t>Ria</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Garchinski</t>
+          <t>Oanes</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>c13garch@gmail.com</t>
+          <t>oaneslaw@gmail.com</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -6477,17 +6477,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Enes</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Guneri</t>
+          <t>Caskie</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>enesgg90@gmail.com</t>
+          <t>jencaskie@gmail.com</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -6499,17 +6499,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Faizah</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Gaya</t>
+          <t>Dekort</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>faizah.gaya@gmail.com</t>
+          <t>jordandekort@gmail.com</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -6521,17 +6521,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Kimberly</t>
+          <t>Don</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Saunders</t>
+          <t>Oanes</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>kimlsaunders@yahoo.ca</t>
+          <t>kamonte311@yahoo.com</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -6543,17 +6543,17 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Brenda</t>
+          <t>Abby</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Tremblay</t>
+          <t>Green</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>brentrem73@gmail.com</t>
+          <t>abby06green@gmail.com</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -6565,17 +6565,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Caleb</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Bilodeau</t>
+          <t>Garchinski</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>emiliebilodeauu@gmail.com</t>
+          <t>c13garch@gmail.com</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -6587,17 +6587,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Luba</t>
+          <t>Enes</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Rudik</t>
+          <t>Guneri</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>lubarudik@yahoo.com</t>
+          <t>enesgg90@gmail.com</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -6609,17 +6609,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Neschelle</t>
+          <t>Faizah</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Prame</t>
+          <t>Gaya</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>neschellelok@yahoo.ca</t>
+          <t>faizah.gaya@gmail.com</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -6631,17 +6631,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Rod</t>
+          <t>Kimberly</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Saunders</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>rodfres26@gmail.com</t>
+          <t>kimlsaunders@yahoo.ca</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -6653,17 +6653,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Fran</t>
+          <t>Brenda</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Tremblay</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>frankcook@mac.com</t>
+          <t>brentrem73@gmail.com</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -6675,17 +6675,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Arvind</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Bilodeau</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>aks9ca@yahoo.com</t>
+          <t>emiliebilodeauu@gmail.com</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -6697,17 +6697,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Val</t>
+          <t>Luba</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>Rudik</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>valandchris@rogers.com</t>
+          <t>lubarudik@yahoo.com</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -6719,17 +6719,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Carali</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>sparkie_jones@hotmail.com</t>
+          <t>georgecarali@yahoo.com</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -6741,17 +6741,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Ashu</t>
+          <t>Neschelle</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Khanna</t>
+          <t>Prame</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>sr71bb99@yahoo.com</t>
+          <t>neschellelok@yahoo.ca</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -6763,17 +6763,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Rita</t>
+          <t>Rod</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Khanna</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>rita.khanna18@yahoo.ca</t>
+          <t>rodfres26@gmail.com</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -6785,17 +6785,17 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Katie</t>
+          <t>Fran</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Todd</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>katieajtodd@gmail.com</t>
+          <t>frankcook@mac.com</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -6807,17 +6807,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Anil</t>
+          <t>Arvind</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Nagpal</t>
+          <t>Sharma</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>a.nagpal@rogers.com</t>
+          <t>aks9ca@yahoo.com</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -6829,17 +6829,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Ristic</t>
+          <t>Seller</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>ristic44@gmail.com</t>
+          <t>valandchris@rogers.com</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -6851,17 +6851,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Ross</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Mcgcoch</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>roscr17@live.ca</t>
+          <t>sparkie_jones@hotmail.com</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -6873,17 +6873,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Cohen</t>
+          <t>Ashu</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Delvecchil</t>
+          <t>Khanna</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>jam_delvecchil@gmail.com</t>
+          <t>sr71bb99@yahoo.com</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -6895,17 +6895,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Rita</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Daly</t>
+          <t>Khanna</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>mikeeee@rogers.com</t>
+          <t>rita.khanna18@yahoo.ca</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -6917,17 +6917,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>janet</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>nolan</t>
+          <t>Todd</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>janetnolan6@hotmail.com</t>
+          <t>katieajtodd@gmail.com</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -6939,7 +6939,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Riya</t>
+          <t>Anil</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -6947,7 +6947,11 @@
           <t>Nagpal</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr"/>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>a.nagpal@rogers.com</t>
+        </is>
+      </c>
       <c r="D325" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -6957,17 +6961,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>preeti</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>wadhwa</t>
+          <t>Ristic</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>preetiwadhwa87@gmail.com</t>
+          <t>ristic44@gmail.com</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -6979,17 +6983,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Ross</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Mcgcoch</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>akcook@carolina.rr.com</t>
+          <t>roscr17@live.ca</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7001,17 +7005,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Cohen</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Anto</t>
+          <t>Delvecchil</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>ranto1993@gmail.com</t>
+          <t>jam_delvecchil@gmail.com</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -7023,17 +7027,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Grahn</t>
+          <t>Daly</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>robjobgrahn@outlook.com</t>
+          <t>mikeeee@rogers.com</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -7045,15 +7049,19 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Riya</t>
+          <t>janet</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Nagpal</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr"/>
+          <t>nolan</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>janetnolan6@hotmail.com</t>
+        </is>
+      </c>
       <c r="D330" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -7063,19 +7071,15 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Riya</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Fernandes</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>all_temp@hotmail.com</t>
-        </is>
-      </c>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -7085,17 +7089,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Vikas</t>
+          <t>preeti</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Sakariya</t>
+          <t>wadhwa</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>sakariyavikas@gmail.com</t>
+          <t>preetiwadhwa87@gmail.com</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -7107,17 +7111,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Lyka</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Fresnedi</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>lykafresnedi@gmail.com</t>
+          <t>akcook@carolina.rr.com</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -7129,17 +7133,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Graeme</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>McMath</t>
+          <t>Anto</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>gtmcmath@gmail.com</t>
+          <t>ranto1993@gmail.com</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -7151,17 +7155,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Fatima</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Seibold</t>
+          <t>Grahn</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>fatimaseibold@hotmail.com</t>
+          <t>robjobgrahn@outlook.com</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -7173,19 +7177,15 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Denise</t>
+          <t>Riya</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Jones</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>denisejanetjones@gmail.com</t>
-        </is>
-      </c>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -7195,17 +7195,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Neal</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Bouwneester</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>nbouwmeester@gmail.com</t>
+          <t>all_temp@hotmail.com</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -7217,17 +7217,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Saurabh</t>
+          <t>Vikas</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Chopra</t>
+          <t>Sakariya</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>schopra86@live.com</t>
+          <t>sakariyavikas@gmail.com</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -7239,17 +7239,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Kristy</t>
+          <t>Lyka</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>MacGregor</t>
+          <t>Fresnedi</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>kristy.hallx@gmail.com</t>
+          <t>lykafresnedi@gmail.com</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -7261,17 +7261,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Chu</t>
+          <t>Graeme</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>McMath</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>tan.chu1997@gmail.com</t>
+          <t>gtmcmath@gmail.com</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Dale</t>
+          <t>Fatima</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>dale.seibold@hotmail.com</t>
+          <t>fatimaseibold@hotmail.com</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -7305,17 +7305,17 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Denise</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Seller</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>valandchris@roger.com</t>
+          <t>denisejanetjones@gmail.com</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -7327,17 +7327,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Neal</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Judges</t>
+          <t>Bouwneester</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>jenniferbattler@gmail.com</t>
+          <t>nbouwmeester@gmail.com</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -7349,17 +7349,17 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Momina</t>
+          <t>Saurabh</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Mir</t>
+          <t>Chopra</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>biological.engineer@gmail.com</t>
+          <t>schopra86@live.com</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -7371,17 +7371,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Tayyab</t>
+          <t>Kristy</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Ahmed</t>
+          <t>MacGregor</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>tayyabahmed561@gmail.com</t>
+          <t>kristy.hallx@gmail.com</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -7393,15 +7393,19 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ansharah</t>
+          <t>Chu</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Abdool</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr"/>
+          <t>Tan</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>tan.chu1997@gmail.com</t>
+        </is>
+      </c>
       <c r="D346" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -7411,17 +7415,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Omar</t>
+          <t>Dale</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Abdool</t>
+          <t>Seibold</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>momina.and.omar@gmail.com</t>
+          <t>dale.seibold@hotmail.com</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -7433,17 +7437,17 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Isla</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Macloud</t>
+          <t>Seller</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>isla20macloud@gmail.com</t>
+          <t>valandchris@roger.com</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -7455,17 +7459,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Cynthis</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Perri</t>
+          <t>Judges</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>cindyp@charcoalgroup.ca</t>
+          <t>jenniferbattler@gmail.com</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -7477,17 +7481,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Saurabh</t>
+          <t>Momina</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Nagpal</t>
+          <t>Mir</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>info@saurabhnagpal.ca</t>
+          <t>biological.engineer@gmail.com</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -7499,17 +7503,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Mansi</t>
+          <t>Tayyab</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Chadha</t>
+          <t>Ahmed</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>mansisegan@gmail.com</t>
+          <t>tayyabahmed561@gmail.com</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -7521,19 +7525,15 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Ansharah</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Barroso</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>l.barroso@live.ca</t>
-        </is>
-      </c>
+          <t>Abdool</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -7543,17 +7543,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Foulds</t>
+          <t>Abdool</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>confirmemail123@gmail.com</t>
+          <t>momina.and.omar@gmail.com</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -7565,17 +7565,17 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Abe</t>
+          <t>Isla</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Macloud</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>abesammac@gmail.com</t>
+          <t>isla20macloud@gmail.com</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -7587,17 +7587,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Jessie</t>
+          <t>Cynthis</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Tang</t>
+          <t>Perri</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>tjting@gmail.com</t>
+          <t>cindyp@charcoalgroup.ca</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -7609,7 +7609,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Mandeep</t>
+          <t>Saurabh</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -7617,7 +7617,11 @@
           <t>Nagpal</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr"/>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>info@saurabhnagpal.ca</t>
+        </is>
+      </c>
       <c r="D356" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -7627,17 +7631,17 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Evan</t>
+          <t>Mansi</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Crossman</t>
+          <t>Chadha</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>caley.crossman@gmail.com</t>
+          <t>mansisegan@gmail.com</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -7649,17 +7653,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Jozsvai</t>
+          <t>Barroso</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>julian_007@hotmail.com</t>
+          <t>l.barroso@live.ca</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -7671,17 +7675,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Gaurav</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Chadha</t>
+          <t>Foulds</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>gauravchadha30@gmail.com</t>
+          <t>confirmemail123@gmail.com</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -7693,17 +7697,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Maeem</t>
+          <t>Abe</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Mir</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>maeemymir@gmail.com</t>
+          <t>abesammac@gmail.com</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -7715,17 +7719,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Mandeep</t>
+          <t>Jessie</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Nagpal</t>
+          <t>Tang</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>nagpalmandeep@icloud.com</t>
+          <t>tjting@gmail.com</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -7737,19 +7741,15 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Mandeep</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Marton</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>joannamarton24@gmail.com</t>
-        </is>
-      </c>
+          <t>Nagpal</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -7759,17 +7759,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Evan</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Burke</t>
+          <t>Crossman</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>jennburke2525@gmail.com</t>
+          <t>caley.crossman@gmail.com</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -7781,17 +7781,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Diane</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Foulds</t>
+          <t>Jozsvai</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>diane.pure@gmail.com</t>
+          <t>julian_007@hotmail.com</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -7803,17 +7803,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Nelo</t>
+          <t>Gaurav</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Tagbacaula</t>
+          <t>Chadha</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>nelo75@yahoo.com</t>
+          <t>gauravchadha30@gmail.com</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -7825,17 +7825,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Trong</t>
+          <t>Maeem</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Hoang</t>
+          <t>Mir</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>trong_227@yahoo.ca</t>
+          <t>maeemymir@gmail.com</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -7847,17 +7847,17 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Barry</t>
+          <t>Mandeep</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Saville</t>
+          <t>Nagpal</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>jbarrysaville@gmail.com</t>
+          <t>nagpalmandeep@icloud.com</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -7869,17 +7869,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Val</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Smith-Sellers</t>
+          <t>Marton</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>vsmithsellers@rogers.com</t>
+          <t>joannamarton24@gmail.com</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -7891,17 +7891,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Ishmam</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Chandan</t>
+          <t>Burke</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>ichandan@septodont.com</t>
+          <t>jennburke2525@gmail.com</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -7913,17 +7913,17 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Chanthala</t>
+          <t>Diane</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Luong</t>
+          <t>Foulds</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>mluong98@hotmail.com</t>
+          <t>diane.pure@gmail.com</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -7935,17 +7935,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Huzaifa</t>
+          <t>Nelo</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Hatia</t>
+          <t>Tagbacaula</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>hatia.huzaifa@icloud.com</t>
+          <t>nelo75@yahoo.com</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -7957,17 +7957,17 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Furqan</t>
+          <t>Trong</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Salam</t>
+          <t>Hoang</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>fsalam@live.com</t>
+          <t>trong_227@yahoo.ca</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -7979,17 +7979,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Sadiq</t>
+          <t>Barry</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Rehman</t>
+          <t>Saville</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>sadiqrehman5@gmail.com</t>
+          <t>jbarrysaville@gmail.com</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -8001,17 +8001,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Moosa</t>
+          <t>Val</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Sedu</t>
+          <t>Smith-Sellers</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>moosa.sedu@yahoo.ca</t>
+          <t>vsmithsellers@rogers.com</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -8023,17 +8023,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Bruno</t>
+          <t>Ishmam</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Semedo</t>
+          <t>Chandan</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>ilovemom_2017@outlook.com</t>
+          <t>ichandan@septodont.com</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -8045,17 +8045,17 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Chanthala</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Sine</t>
+          <t>Luong</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>jacobofsine@hotmail.com</t>
+          <t>mluong98@hotmail.com</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -8067,17 +8067,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Jayce</t>
+          <t>Huzaifa</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Semedo</t>
+          <t>Hatia</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>ilovelmom_2017@outlook.com</t>
+          <t>hatia.huzaifa@icloud.com</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -8089,17 +8089,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Tracy</t>
+          <t>Furqan</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Watters</t>
+          <t>Salam</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>tracy.watters@hotmail.com</t>
+          <t>fsalam@live.com</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -8111,17 +8111,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Sadiq</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Melichercik</t>
+          <t>Rehman</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>jmeliche@uoguelph.ca</t>
+          <t>sadiqrehman5@gmail.com</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -8133,17 +8133,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Lindsay</t>
+          <t>Pranil</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Ravi</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>lindsay.kennedy2797@gmail.com</t>
+          <t>pranm97@gmail.com</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -8155,17 +8155,17 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Dennis</t>
+          <t>Moosa</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Cabrera</t>
+          <t>Sedu</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>denniscabrera231@gmail.com</t>
+          <t>moosa.sedu@yahoo.ca</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -8177,17 +8177,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>Bruno</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Sherriff</t>
+          <t>Semedo</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>quiettime90@hotmail.com</t>
+          <t>ilovemom_2017@outlook.com</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -8199,17 +8199,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Braeden</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Snyder</t>
+          <t>Sine</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>braeden.snyder@live.com</t>
+          <t>jacobofsine@hotmail.com</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -8221,17 +8221,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Jayce</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Watters</t>
+          <t>Semedo</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>gwatters@live.com</t>
+          <t>ilovelmom_2017@outlook.com</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -8243,17 +8243,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Tracy</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Melichercik</t>
+          <t>Watters</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>markmelichercik@gmail.com</t>
+          <t>tracy.watters@hotmail.com</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -8265,17 +8265,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Paddock</t>
+          <t>Melichercik</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>ethan.paddock@gmail.com</t>
+          <t>jmeliche@uoguelph.ca</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -8287,17 +8287,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Lindsay</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Soucie</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>ben.soucie@me.com</t>
+          <t>lindsay.kennedy2797@gmail.com</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -8309,17 +8309,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Devansh</t>
+          <t>Dennis</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Mehta</t>
+          <t>Cabrera</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>d33mehta@uwaterloo.ca</t>
+          <t>denniscabrera231@gmail.com</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -8331,17 +8331,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Rohan</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Gambhir</t>
+          <t>Sherriff</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>rohan.gambhir786@gmail.com</t>
+          <t>quiettime90@hotmail.com</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -8353,17 +8353,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Anweshika</t>
+          <t>Braeden</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Anweshika</t>
+          <t>Snyder</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>anweshika.gec@gmail.com</t>
+          <t>braeden.snyder@live.com</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -8375,15 +8375,19 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Evelyn</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr"/>
+          <t>Watters</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>gwatters@live.com</t>
+        </is>
+      </c>
       <c r="D391" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -8393,17 +8397,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Atkinson</t>
+          <t>Melichercik</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>leecatkinson@gmail.com</t>
+          <t>markmelichercik@gmail.com</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -8415,17 +8419,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Mann</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Mann</t>
+          <t>Paddock</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>vishal.mann33@gmail.com</t>
+          <t>ethan.paddock@gmail.com</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -8437,17 +8441,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Saurabh</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Soucie</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>saurabhsingh@gmail.com</t>
+          <t>ben.soucie@me.com</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -8459,17 +8463,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Kathryn</t>
+          <t>Devansh</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Emms</t>
+          <t>Mehta</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>kathrynemms@me.com</t>
+          <t>d33mehta@uwaterloo.ca</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -8481,17 +8485,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Rohan</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Atienza</t>
+          <t>Gambhir</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>alexandra.g.atienza@gmail.com</t>
+          <t>rohan.gambhir786@gmail.com</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -8503,17 +8507,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Kyle</t>
+          <t>Anweshika</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>oei</t>
+          <t>Anweshika</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>kyleoei2787@gmail.com</t>
+          <t>anweshika.gec@gmail.com</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -8525,19 +8529,15 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Manoocehri</t>
-        </is>
-      </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>lapd1356@gmail.com</t>
-        </is>
-      </c>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
@@ -8547,17 +8547,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Ashley</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Schembri</t>
+          <t>Atkinson</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>ashley.schembri@gmail.com</t>
+          <t>leecatkinson@gmail.com</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -8569,17 +8569,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>Mann</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Atkinson</t>
+          <t>Mann</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>dougatkinson32@gmail.com</t>
+          <t>vishal.mann33@gmail.com</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -8591,20 +8591,1998 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
+          <t>Saurabh</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Singh</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>saurabhsingh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Kathryn</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Emms</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>kathrynemms@me.com</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Alexandra</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Atienza</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>alexandra.g.atienza@gmail.com</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Kyle</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>oei</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>kyleoei2787@gmail.com</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Dave</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Manoocehri</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>lapd1356@gmail.com</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Schembri</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>ashley.schembri@gmail.com</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Doug</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Atkinson</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>dougatkinson32@gmail.com</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
           <t>Linda</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
+      <c r="B408" t="inlineStr">
         <is>
           <t>Innanen</t>
         </is>
       </c>
-      <c r="C401" t="inlineStr">
+      <c r="C408" t="inlineStr">
         <is>
           <t>linda.innanen@gmail.com</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr">
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Kim</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Bigam</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>kbigam12@gmail.com</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Michelle</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Kings</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>michellekings@gmail.com</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Steve</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Parr</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>sparr@duck.com</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Jason</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Nazareth</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>janazareth@duck.com</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Leighton</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Colleen</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Klein</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>kozmokat@gmail.com</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Furqan</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Gaya</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>fgaya123@gmail.com</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Aaron</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Leighton</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Carson</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Wright</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>carson.wright77@icloud.com</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Harrington</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>qxg6@outlook.com</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>stefany</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>roccasecca</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>stefanyroccasecca@icloud.com</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Saj</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Karim</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>skarim@cgf.com</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Talia</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Klein Leighton</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>taliarklein@gmail.com</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Luciana</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Medeiros Da Silva</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>luciana.medeiros@live.com</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Kirsten</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Lewis</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>kirstencar@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Jim</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Bietio</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>jim.bietio@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Ardith</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Inapan</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>ardithinapan@gmail.com</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Art</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Bazoian - trial</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>triplebogey2804@hotmail.ca</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Filomena</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Fernandes</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>fil-cesar@rogers.com.com</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Nicolas</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>ntsantos2001@gmail.com</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Vicki</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Nickless</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>vnickless21@gmail.com</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Jeff</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Gordon</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>jgordon297@bell.net</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Bruno</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Semedo</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>ilovemoney_2017@outlook.com</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>thanvish</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>sabapathee</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Maggie</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Watson</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>watson_m@live.com</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>mark</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Medeiros Da Silva</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>mdemmery@roger.com</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>fiona</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>macgregor</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>fmac@sympatico.ca</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>koyel</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>sabapathee</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Belinda</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Lutes</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>dolphins@rogers.com</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Dominic</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Diraddo</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>domdiraddo@gmail.com</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Shannon</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Ahola</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>aloha77@yahoo.com</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Meg</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Artymko</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>margaret_curtis@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Shelley</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Fitzpatrick</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>shelley.fitzpatrick9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Amaral</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>alex_aamaral06@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Demmery</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>mdemmery@rogers.com</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Lambert</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>stephaniewinger@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Rory</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Campbell</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>rorydcampbell@gmail.com</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Brennan</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Campbell</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>brennancampbell@gmail.com</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>andre</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>templeton</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>andre@kwreg.ca</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Pichayapa</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Ieadkaew</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>pichayapaieadkaew@gmail.com</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Ryan</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>ryanmartin@rogers.com</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Terri</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Luu</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>terriluu6674@gmail.com</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Noi</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Phonechaleon</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>noiphonechaleon@gmail.com</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Tao</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>taoniken2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Cameron</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Hattie</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>camerongattie291@gmail.com</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Anthony</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Ceccomancini</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>tonyceccomancini@gmail.com</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Noreiga</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>chrisnoreiga23@gmail.com</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Huzaifa</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Darsot</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>huzaifadarsot2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Donna</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Mackie</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>dmackiefam@gmail.com</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Madi</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Atkins</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>madi.atkins77@icloud.com</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Rocco</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>rocco.p2006@icloud.com</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Keith</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Mackie</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>keithmackie9@gmail.com</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>Jaden</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Downs</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>joaden.downs2004@gmail.com</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Ke</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>DING</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>taonike6@gmail.com</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Talhah</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Hansrod</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>talhah8681@gmail.com</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Cameron</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Wright</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>camwright22@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>sammy.p2004@icloud.com</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Phung</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>avocadoughh@gmail.com</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Julie</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Downs</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>juliedowns2003@gmail.com</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Tawseef</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Unia</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>tawseef.unia@gmail.com</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Irving</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Ding</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>irvding@gmail.com</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Sunny</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Li</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>lhn20082012@gmail.com</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Alex</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Luu</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>alexpluu7@gmail.com</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Aspinall</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>jaspinall@crsuntours.com</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Theodore</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Davison</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Finley</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Davison</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>Terrie</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Racine</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>terrieracine66@gmail.edu</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Nina</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Cruz</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>nina.p.cruz@gmail.com</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Bob</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Downey</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>jaime.downey3@gmail.com</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Bout</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>hbout@protonmail.com</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Vivek</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Mahesh</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>vivekcm24@gmail.com</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Naleefa</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Zubair</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>senaumma1924@gmail.com</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Jesette</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Rubio</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>jesette.rubio@gmail.com</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Jaime</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Downey</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>jaime.downey@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Christie</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Downey</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>christie.downey@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Naomi</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Angod</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>naaomik@gmail.com</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Ibnu</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Mahmood</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>znzth@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Josh</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Tiggelman</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>tiggleman98@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Ben</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Seper</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>beyamin340@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Derrick</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Racine</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>dracine@uwf.edu</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Davison</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>michael.a.davison@gmail.com</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Ashwani</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Kapur</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>ashwanikapurca@yahoo.ca</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Isaac</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Zylbering</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>eyedzee@hotmail.com</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>cambridge@pickleplex.ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Amanda</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Davison</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>amandachristine19@gmail.com</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
         <is>
           <t>cambridge@pickleplex.ca</t>
         </is>
